--- a/Dentist_Module_Map.xlsx
+++ b/Dentist_Module_Map.xlsx
@@ -12,10 +12,11 @@
     <sheet name="Module Map" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Module List" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="Screen Inventory" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Change Log" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Module List'!$A$4:$I$113</definedName>
-    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">'Screen Inventory'!$A$4:$I$87</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Module List'!$A$4:$I$118</definedName>
+    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">'Screen Inventory'!$A$4:$I$93</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1596" uniqueCount="546">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1711" uniqueCount="587">
   <si>
     <t xml:space="preserve">Summary by Module</t>
   </si>
@@ -312,7 +313,22 @@
     <t xml:space="preserve">M03.07.02  Add transaction · type</t>
   </si>
   <si>
-    <t xml:space="preserve">M03.07.03  Add transaction · procedure</t>
+    <t xml:space="preserve">M03.07.03  Procedure transaction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M03.07.04  Add procedure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M03.07.05  Browse all procedures</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M03.07.06  Purchase item transaction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M03.07.07  Add item</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M03.07.08  Browse all items</t>
   </si>
   <si>
     <t xml:space="preserve">M03.08  Statement of Account</t>
@@ -1049,10 +1065,55 @@
     <t xml:space="preserve">M03.07.03</t>
   </si>
   <si>
-    <t xml:space="preserve">Add transaction · procedure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enter procedure line items.</t>
+    <t xml:space="preserve">Procedure transaction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New procedure form: line items with procedure, tooth no., cost, discount and total; search-as-you-type for procedures; Save transaction.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M03.07.04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add procedure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add a procedure line with tooth no., cost, discount and total cost.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M03.07.05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Browse all procedures</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full procedure catalogue with prices to pick from.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M03.07.06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Purchase item transaction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New purchase form: items with quantity and unit price; Save transaction.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M03.07.07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add item</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add a purchase item line.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M03.07.08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Browse all items</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Item catalogue with stock and price to pick from.</t>
   </si>
   <si>
     <t xml:space="preserve">M03.08</t>
@@ -1550,7 +1611,25 @@
     <t xml:space="preserve">Patients — Details · Transaction Record · Add transaction · Transaction type · Layout B · Desktop</t>
   </si>
   <si>
-    <t xml:space="preserve">Patients — Details · Transaction Record · Add transaction · Procedure · Desktop</t>
+    <t xml:space="preserve">Patients — Details · Transaction Record · Add transaction · Procedure · Layout B · Desktop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patients — Details · Transaction Record · Add transaction · Procedure · Layout B · Typing a procedure · Desktop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patients — Details · Transaction Record · Add transaction · Procedure · Add procedure · Desktop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patients — Details · Transaction Record · Add transaction · Procedure · Add procedure · All procedures · Desktop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patients — Details · Transaction Record · Add transaction · Purchase Item · Desktop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patients — Details · Transaction Record · Add transaction · Purchase Item · Add item · Desktop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patients — Details · Transaction Record · Add transaction · Purchase Item · Add item · All items · Desktop</t>
   </si>
   <si>
     <t xml:space="preserve">Patients — Details · Statement of Account · Layout B · Desktop</t>
@@ -1671,6 +1750,51 @@
   </si>
   <si>
     <t xml:space="preserve">Profile — Account · My signature · Remove confirmation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Change Log</t>
+  </si>
+  <si>
+    <t xml:space="preserve">History of updates to this workbook.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Version</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Module / Area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Change</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oct 11, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First version: 6 modules, 20 sub-modules, 83 features, 83 screens.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Figma frames were recreated, so every frame ID changed. All Figma links now point to the new frames.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M03.07 Transaction Record</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Replaced 'Add transaction · procedure' with 6 features: Procedure transaction, Add procedure, Browse all procedures, Purchase item transaction, Add item, Browse all items.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Screens: 1 old 'Add transaction · Procedure' frame replaced by 7 new frames (Procedure ×4, Purchase Item ×3). Total features 83 → 88, total screens 83 → 89.</t>
   </si>
 </sst>
 </file>
@@ -2551,11 +2675,11 @@
       </c>
       <c r="D8" s="4" t="n">
         <f aca="false">COUNTIFS('Module List'!$A:$A,"M03.*",'Module List'!$B:$B,"Feature")</f>
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E8" s="4" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$B:$B,"M03")</f>
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2608,11 +2732,11 @@
       </c>
       <c r="D11" s="6" t="n">
         <f aca="false">SUM(D5:D10)</f>
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="E11" s="6" t="n">
         <f aca="false">SUM(E5:E10)</f>
-        <v>83</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -2635,7 +2759,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E89"/>
+  <dimension ref="A1:E94"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
@@ -3384,13 +3508,13 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="24"/>
-      <c r="B55" s="25"/>
+      <c r="B55" s="24"/>
       <c r="C55" s="26" t="s">
         <v>93</v>
       </c>
       <c r="D55" s="27" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.07.03")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E55" s="28" t="s">
         <v>35</v>
@@ -3398,30 +3522,26 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="24"/>
-      <c r="B56" s="25" t="s">
+      <c r="B56" s="24"/>
+      <c r="C56" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="C56" s="26" t="s">
+      <c r="D56" s="27" t="n">
+        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.07.04")</f>
+        <v>1</v>
+      </c>
+      <c r="E56" s="28" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="24"/>
+      <c r="B57" s="24"/>
+      <c r="C57" s="26" t="s">
         <v>95</v>
       </c>
-      <c r="D56" s="27" t="n">
-        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.08.01")</f>
-        <v>1</v>
-      </c>
-      <c r="E56" s="28" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="24"/>
-      <c r="B57" s="25" t="s">
-        <v>96</v>
-      </c>
-      <c r="C57" s="26" t="s">
-        <v>97</v>
-      </c>
       <c r="D57" s="27" t="n">
-        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.09.01")</f>
+        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.07.05")</f>
         <v>1</v>
       </c>
       <c r="E57" s="28" t="s">
@@ -3432,10 +3552,10 @@
       <c r="A58" s="24"/>
       <c r="B58" s="24"/>
       <c r="C58" s="26" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D58" s="27" t="n">
-        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.09.02")</f>
+        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.07.06")</f>
         <v>1</v>
       </c>
       <c r="E58" s="28" t="s">
@@ -3446,10 +3566,10 @@
       <c r="A59" s="24"/>
       <c r="B59" s="24"/>
       <c r="C59" s="26" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D59" s="27" t="n">
-        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.09.03")</f>
+        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.07.07")</f>
         <v>1</v>
       </c>
       <c r="E59" s="28" t="s">
@@ -3458,12 +3578,12 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="24"/>
-      <c r="B60" s="24"/>
+      <c r="B60" s="25"/>
       <c r="C60" s="26" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D60" s="27" t="n">
-        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.09.04")</f>
+        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.07.08")</f>
         <v>1</v>
       </c>
       <c r="E60" s="28" t="s">
@@ -3472,26 +3592,30 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="24"/>
-      <c r="B61" s="24"/>
+      <c r="B61" s="25" t="s">
+        <v>99</v>
+      </c>
       <c r="C61" s="26" t="s">
+        <v>100</v>
+      </c>
+      <c r="D61" s="27" t="n">
+        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.08.01")</f>
+        <v>1</v>
+      </c>
+      <c r="E61" s="28" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="24"/>
+      <c r="B62" s="25" t="s">
         <v>101</v>
       </c>
-      <c r="D61" s="27" t="n">
-        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.09.05")</f>
-        <v>1</v>
-      </c>
-      <c r="E61" s="28" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="24"/>
-      <c r="B62" s="24"/>
       <c r="C62" s="26" t="s">
         <v>102</v>
       </c>
       <c r="D62" s="27" t="n">
-        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.09.06")</f>
+        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.09.01")</f>
         <v>1</v>
       </c>
       <c r="E62" s="28" t="s">
@@ -3505,8 +3629,8 @@
         <v>103</v>
       </c>
       <c r="D63" s="27" t="n">
-        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.09.07")</f>
-        <v>3</v>
+        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.09.02")</f>
+        <v>1</v>
       </c>
       <c r="E63" s="28" t="s">
         <v>35</v>
@@ -3519,7 +3643,7 @@
         <v>104</v>
       </c>
       <c r="D64" s="27" t="n">
-        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.09.08")</f>
+        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.09.03")</f>
         <v>1</v>
       </c>
       <c r="E64" s="28" t="s">
@@ -3528,29 +3652,27 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="24"/>
-      <c r="B65" s="25"/>
+      <c r="B65" s="24"/>
       <c r="C65" s="26" t="s">
         <v>105</v>
       </c>
       <c r="D65" s="27" t="n">
-        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.09.09")</f>
+        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.09.04")</f>
         <v>1</v>
       </c>
       <c r="E65" s="28" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="24"/>
-      <c r="B66" s="25" t="s">
+      <c r="B66" s="24"/>
+      <c r="C66" s="26" t="s">
         <v>106</v>
       </c>
-      <c r="C66" s="26" t="s">
-        <v>107</v>
-      </c>
       <c r="D66" s="27" t="n">
-        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.10.01")</f>
-        <v>2</v>
+        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.09.05")</f>
+        <v>1</v>
       </c>
       <c r="E66" s="28" t="s">
         <v>35</v>
@@ -3560,11 +3682,11 @@
       <c r="A67" s="24"/>
       <c r="B67" s="24"/>
       <c r="C67" s="26" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D67" s="27" t="n">
-        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.10.02")</f>
-        <v>2</v>
+        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.09.06")</f>
+        <v>1</v>
       </c>
       <c r="E67" s="28" t="s">
         <v>35</v>
@@ -3574,11 +3696,11 @@
       <c r="A68" s="24"/>
       <c r="B68" s="24"/>
       <c r="C68" s="26" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D68" s="27" t="n">
-        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.10.03")</f>
-        <v>1</v>
+        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.09.07")</f>
+        <v>3</v>
       </c>
       <c r="E68" s="28" t="s">
         <v>35</v>
@@ -3588,218 +3710,218 @@
       <c r="A69" s="24"/>
       <c r="B69" s="24"/>
       <c r="C69" s="26" t="s">
+        <v>109</v>
+      </c>
+      <c r="D69" s="27" t="n">
+        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.09.08")</f>
+        <v>1</v>
+      </c>
+      <c r="E69" s="28" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="24"/>
+      <c r="B70" s="25"/>
+      <c r="C70" s="26" t="s">
         <v>110</v>
       </c>
-      <c r="D69" s="27" t="n">
+      <c r="D70" s="27" t="n">
+        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.09.09")</f>
+        <v>1</v>
+      </c>
+      <c r="E70" s="28" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="24"/>
+      <c r="B71" s="25" t="s">
+        <v>111</v>
+      </c>
+      <c r="C71" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="D71" s="27" t="n">
+        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.10.01")</f>
+        <v>2</v>
+      </c>
+      <c r="E71" s="28" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="24"/>
+      <c r="B72" s="24"/>
+      <c r="C72" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="D72" s="27" t="n">
+        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.10.02")</f>
+        <v>2</v>
+      </c>
+      <c r="E72" s="28" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="24"/>
+      <c r="B73" s="24"/>
+      <c r="C73" s="26" t="s">
+        <v>114</v>
+      </c>
+      <c r="D73" s="27" t="n">
+        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.10.03")</f>
+        <v>1</v>
+      </c>
+      <c r="E73" s="28" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="24"/>
+      <c r="B74" s="24"/>
+      <c r="C74" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="D74" s="27" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.10.04")</f>
         <v>3</v>
       </c>
-      <c r="E69" s="28" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="24"/>
-      <c r="B70" s="24"/>
-      <c r="C70" s="26" t="s">
-        <v>111</v>
-      </c>
-      <c r="D70" s="27" t="n">
+      <c r="E74" s="28" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="24"/>
+      <c r="B75" s="24"/>
+      <c r="C75" s="26" t="s">
+        <v>116</v>
+      </c>
+      <c r="D75" s="27" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.10.05")</f>
         <v>3</v>
       </c>
-      <c r="E70" s="28" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="30" t="s">
-        <v>112</v>
-      </c>
-      <c r="B71" s="31" t="s">
-        <v>113</v>
-      </c>
-      <c r="C71" s="32" t="s">
-        <v>114</v>
-      </c>
-      <c r="D71" s="33" t="n">
+      <c r="E75" s="28" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="B76" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="C76" s="32" t="s">
+        <v>119</v>
+      </c>
+      <c r="D76" s="33" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M04.01.01")</f>
         <v>1</v>
       </c>
-      <c r="E71" s="34" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="30"/>
-      <c r="B72" s="30"/>
-      <c r="C72" s="32" t="s">
-        <v>115</v>
-      </c>
-      <c r="D72" s="33" t="n">
+      <c r="E76" s="34" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="30"/>
+      <c r="B77" s="30"/>
+      <c r="C77" s="32" t="s">
+        <v>120</v>
+      </c>
+      <c r="D77" s="33" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M04.01.02")</f>
         <v>1</v>
       </c>
-      <c r="E72" s="34" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="30"/>
-      <c r="B73" s="30"/>
-      <c r="C73" s="32" t="s">
-        <v>116</v>
-      </c>
-      <c r="D73" s="33" t="n">
+      <c r="E77" s="34" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="30"/>
+      <c r="B78" s="30"/>
+      <c r="C78" s="32" t="s">
+        <v>121</v>
+      </c>
+      <c r="D78" s="33" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M04.01.03")</f>
         <v>1</v>
       </c>
-      <c r="E73" s="34" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="30"/>
-      <c r="B74" s="30"/>
-      <c r="C74" s="32" t="s">
-        <v>117</v>
-      </c>
-      <c r="D74" s="33" t="n">
+      <c r="E78" s="34" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="30"/>
+      <c r="B79" s="30"/>
+      <c r="C79" s="32" t="s">
+        <v>122</v>
+      </c>
+      <c r="D79" s="33" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M04.01.04")</f>
         <v>1</v>
       </c>
-      <c r="E74" s="34" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="30"/>
-      <c r="B75" s="31"/>
-      <c r="C75" s="32" t="s">
-        <v>118</v>
-      </c>
-      <c r="D75" s="33" t="n">
+      <c r="E79" s="34" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="30"/>
+      <c r="B80" s="31"/>
+      <c r="C80" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="D80" s="33" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M04.01.05")</f>
         <v>1</v>
       </c>
-      <c r="E75" s="34" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="30"/>
-      <c r="B76" s="31" t="s">
-        <v>119</v>
-      </c>
-      <c r="C76" s="32" t="s">
-        <v>120</v>
-      </c>
-      <c r="D76" s="33" t="n">
+      <c r="E80" s="34" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="30"/>
+      <c r="B81" s="31" t="s">
+        <v>124</v>
+      </c>
+      <c r="C81" s="32" t="s">
+        <v>125</v>
+      </c>
+      <c r="D81" s="33" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M04.02.01")</f>
         <v>1</v>
       </c>
-      <c r="E76" s="34" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="35" t="s">
-        <v>121</v>
-      </c>
-      <c r="B77" s="36" t="s">
-        <v>122</v>
-      </c>
-      <c r="C77" s="37" t="s">
-        <v>123</v>
-      </c>
-      <c r="D77" s="38" t="n">
-        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M05.01.01")</f>
-        <v>1</v>
-      </c>
-      <c r="E77" s="39" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="35"/>
-      <c r="B78" s="35"/>
-      <c r="C78" s="37" t="s">
-        <v>124</v>
-      </c>
-      <c r="D78" s="38" t="n">
-        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M05.01.02")</f>
-        <v>1</v>
-      </c>
-      <c r="E78" s="39" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="35"/>
-      <c r="B79" s="35"/>
-      <c r="C79" s="37" t="s">
-        <v>125</v>
-      </c>
-      <c r="D79" s="38" t="n">
-        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M05.01.03")</f>
-        <v>1</v>
-      </c>
-      <c r="E79" s="39" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="35"/>
-      <c r="B80" s="35"/>
-      <c r="C80" s="37" t="s">
+      <c r="E81" s="34" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="35" t="s">
         <v>126</v>
       </c>
-      <c r="D80" s="38" t="n">
-        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M05.01.04")</f>
-        <v>1</v>
-      </c>
-      <c r="E80" s="39" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="35"/>
-      <c r="B81" s="35"/>
-      <c r="C81" s="37" t="s">
+      <c r="B82" s="36" t="s">
         <v>127</v>
       </c>
-      <c r="D81" s="38" t="n">
-        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M05.01.05")</f>
-        <v>1</v>
-      </c>
-      <c r="E81" s="39" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="35"/>
-      <c r="B82" s="36"/>
       <c r="C82" s="37" t="s">
         <v>128</v>
       </c>
       <c r="D82" s="38" t="n">
-        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M05.01.06")</f>
+        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M05.01.01")</f>
         <v>1</v>
       </c>
       <c r="E82" s="39" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="35"/>
-      <c r="B83" s="36" t="s">
+      <c r="B83" s="35"/>
+      <c r="C83" s="37" t="s">
         <v>129</v>
       </c>
-      <c r="C83" s="37" t="s">
-        <v>130</v>
-      </c>
       <c r="D83" s="38" t="n">
-        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M05.02.01")</f>
+        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M05.01.02")</f>
         <v>1</v>
       </c>
       <c r="E83" s="39" t="s">
@@ -3810,10 +3932,10 @@
       <c r="A84" s="35"/>
       <c r="B84" s="35"/>
       <c r="C84" s="37" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D84" s="38" t="n">
-        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M05.02.02")</f>
+        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M05.01.03")</f>
         <v>1</v>
       </c>
       <c r="E84" s="39" t="s">
@@ -3824,10 +3946,10 @@
       <c r="A85" s="35"/>
       <c r="B85" s="35"/>
       <c r="C85" s="37" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D85" s="38" t="n">
-        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M05.02.03")</f>
+        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M05.01.04")</f>
         <v>1</v>
       </c>
       <c r="E85" s="39" t="s">
@@ -3838,10 +3960,10 @@
       <c r="A86" s="35"/>
       <c r="B86" s="35"/>
       <c r="C86" s="37" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D86" s="38" t="n">
-        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M05.02.04")</f>
+        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M05.01.05")</f>
         <v>1</v>
       </c>
       <c r="E86" s="39" t="s">
@@ -3850,30 +3972,102 @@
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="35"/>
-      <c r="B87" s="35"/>
+      <c r="B87" s="36"/>
       <c r="C87" s="37" t="s">
+        <v>133</v>
+      </c>
+      <c r="D87" s="38" t="n">
+        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M05.01.06")</f>
+        <v>1</v>
+      </c>
+      <c r="E87" s="39" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A88" s="35"/>
+      <c r="B88" s="36" t="s">
         <v>134</v>
       </c>
-      <c r="D87" s="38" t="n">
+      <c r="C88" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="D88" s="38" t="n">
+        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M05.02.01")</f>
+        <v>1</v>
+      </c>
+      <c r="E88" s="39" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="35"/>
+      <c r="B89" s="35"/>
+      <c r="C89" s="37" t="s">
+        <v>136</v>
+      </c>
+      <c r="D89" s="38" t="n">
+        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M05.02.02")</f>
+        <v>1</v>
+      </c>
+      <c r="E89" s="39" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="35"/>
+      <c r="B90" s="35"/>
+      <c r="C90" s="37" t="s">
+        <v>137</v>
+      </c>
+      <c r="D90" s="38" t="n">
+        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M05.02.03")</f>
+        <v>1</v>
+      </c>
+      <c r="E90" s="39" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="35"/>
+      <c r="B91" s="35"/>
+      <c r="C91" s="37" t="s">
+        <v>138</v>
+      </c>
+      <c r="D91" s="38" t="n">
+        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M05.02.04")</f>
+        <v>1</v>
+      </c>
+      <c r="E91" s="39" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="35"/>
+      <c r="B92" s="35"/>
+      <c r="C92" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="D92" s="38" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M05.02.05")</f>
         <v>1</v>
       </c>
-      <c r="E87" s="39" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C88" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="D88" s="40" t="n">
-        <f aca="false">SUM(D5:D87)</f>
-        <v>83</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="41" t="s">
-        <v>136</v>
+      <c r="E92" s="39" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C93" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="D93" s="40" t="n">
+        <f aca="false">SUM(D5:D92)</f>
+        <v>89</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="41" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -3889,20 +4083,20 @@
     <mergeCell ref="B22:B28"/>
     <mergeCell ref="B29:B33"/>
     <mergeCell ref="B34:B35"/>
-    <mergeCell ref="A36:A70"/>
+    <mergeCell ref="A36:A75"/>
     <mergeCell ref="B37:B41"/>
     <mergeCell ref="B42:B45"/>
     <mergeCell ref="B46:B47"/>
     <mergeCell ref="B48:B49"/>
     <mergeCell ref="B50:B52"/>
-    <mergeCell ref="B53:B55"/>
-    <mergeCell ref="B57:B65"/>
-    <mergeCell ref="B66:B70"/>
-    <mergeCell ref="A71:A76"/>
+    <mergeCell ref="B53:B60"/>
+    <mergeCell ref="B62:B70"/>
     <mergeCell ref="B71:B75"/>
-    <mergeCell ref="A77:A87"/>
-    <mergeCell ref="B77:B82"/>
-    <mergeCell ref="B83:B87"/>
+    <mergeCell ref="A76:A81"/>
+    <mergeCell ref="B76:B80"/>
+    <mergeCell ref="A82:A92"/>
+    <mergeCell ref="B82:B87"/>
+    <mergeCell ref="B88:B92"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E10" r:id="rId1" display="Open"/>
@@ -3972,6 +4166,11 @@
     <hyperlink ref="E85" r:id="rId65" display="Open"/>
     <hyperlink ref="E86" r:id="rId66" display="Open"/>
     <hyperlink ref="E87" r:id="rId67" display="Open"/>
+    <hyperlink ref="E88" r:id="rId68" display="Open"/>
+    <hyperlink ref="E89" r:id="rId69" display="Open"/>
+    <hyperlink ref="E90" r:id="rId70" display="Open"/>
+    <hyperlink ref="E91" r:id="rId71" display="Open"/>
+    <hyperlink ref="E92" r:id="rId72" display="Open"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3988,7 +4187,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I113"/>
+  <dimension ref="A1:I118"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -4004,7 +4203,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4030,10 +4229,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>3</v>
@@ -4045,16 +4244,16 @@
         <v>23</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>6</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4070,7 +4269,7 @@
       <c r="D5" s="42"/>
       <c r="E5" s="42"/>
       <c r="F5" s="42" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="G5" s="43" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$B:$B,"M00")</f>
@@ -4081,7 +4280,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="44" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="B6" s="44" t="s">
         <v>22</v>
@@ -4090,11 +4289,11 @@
         <v>8</v>
       </c>
       <c r="D6" s="44" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="E6" s="44"/>
       <c r="F6" s="44" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="G6" s="45" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$D:$D,"M00.01")</f>
@@ -4105,7 +4304,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="46" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="B7" s="46" t="s">
         <v>23</v>
@@ -4114,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="D7" s="46" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="E7" s="46" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="F7" s="46" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="G7" s="47" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M00.01.01")</f>
@@ -4128,12 +4327,12 @@
       </c>
       <c r="H7" s="46"/>
       <c r="I7" s="46" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="46" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="B8" s="46" t="s">
         <v>23</v>
@@ -4142,13 +4341,13 @@
         <v>8</v>
       </c>
       <c r="D8" s="46" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="E8" s="46" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="F8" s="46" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="G8" s="47" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M00.01.02")</f>
@@ -4156,12 +4355,12 @@
       </c>
       <c r="H8" s="46"/>
       <c r="I8" s="46" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="46" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="B9" s="46" t="s">
         <v>23</v>
@@ -4170,13 +4369,13 @@
         <v>8</v>
       </c>
       <c r="D9" s="46" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="E9" s="46" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="F9" s="46" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="G9" s="47" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M00.01.03")</f>
@@ -4184,12 +4383,12 @@
       </c>
       <c r="H9" s="46"/>
       <c r="I9" s="46" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="46" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="B10" s="46" t="s">
         <v>23</v>
@@ -4198,13 +4397,13 @@
         <v>8</v>
       </c>
       <c r="D10" s="46" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="E10" s="46" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="F10" s="46" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="G10" s="47" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M00.01.04")</f>
@@ -4212,12 +4411,12 @@
       </c>
       <c r="H10" s="46"/>
       <c r="I10" s="46" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="46" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B11" s="46" t="s">
         <v>23</v>
@@ -4226,13 +4425,13 @@
         <v>8</v>
       </c>
       <c r="D11" s="46" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="E11" s="46" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="F11" s="46" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="G11" s="47" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M00.01.05")</f>
@@ -4240,7 +4439,7 @@
       </c>
       <c r="H11" s="46"/>
       <c r="I11" s="46" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4256,7 +4455,7 @@
       <c r="D12" s="48"/>
       <c r="E12" s="48"/>
       <c r="F12" s="48" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="G12" s="49" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$B:$B,"M01")</f>
@@ -4267,7 +4466,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="44" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B13" s="44" t="s">
         <v>22</v>
@@ -4276,11 +4475,11 @@
         <v>10</v>
       </c>
       <c r="D13" s="44" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="E13" s="44"/>
       <c r="F13" s="44" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="G13" s="45" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$D:$D,"M01.01")</f>
@@ -4291,7 +4490,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="46" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B14" s="46" t="s">
         <v>23</v>
@@ -4300,13 +4499,13 @@
         <v>10</v>
       </c>
       <c r="D14" s="46" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="E14" s="46" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="F14" s="46" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="G14" s="47" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M01.01.01")</f>
@@ -4319,7 +4518,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="46" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="B15" s="46" t="s">
         <v>23</v>
@@ -4328,13 +4527,13 @@
         <v>10</v>
       </c>
       <c r="D15" s="46" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="E15" s="46" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="F15" s="46" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="G15" s="47" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M01.01.02")</f>
@@ -4342,12 +4541,12 @@
       </c>
       <c r="H15" s="46"/>
       <c r="I15" s="46" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="46" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="B16" s="46" t="s">
         <v>23</v>
@@ -4356,13 +4555,13 @@
         <v>10</v>
       </c>
       <c r="D16" s="46" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="E16" s="46" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="F16" s="46" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G16" s="47" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M01.01.03")</f>
@@ -4370,12 +4569,12 @@
       </c>
       <c r="H16" s="46"/>
       <c r="I16" s="46" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="46" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="B17" s="46" t="s">
         <v>23</v>
@@ -4384,13 +4583,13 @@
         <v>10</v>
       </c>
       <c r="D17" s="46" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="E17" s="46" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="F17" s="46" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="G17" s="47" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M01.01.04")</f>
@@ -4398,12 +4597,12 @@
       </c>
       <c r="H17" s="46"/>
       <c r="I17" s="46" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="46" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="B18" s="46" t="s">
         <v>23</v>
@@ -4412,13 +4611,13 @@
         <v>10</v>
       </c>
       <c r="D18" s="46" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="E18" s="46" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="F18" s="46" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="G18" s="47" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M01.01.05")</f>
@@ -4426,12 +4625,12 @@
       </c>
       <c r="H18" s="46"/>
       <c r="I18" s="46" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="46" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="B19" s="46" t="s">
         <v>23</v>
@@ -4440,13 +4639,13 @@
         <v>10</v>
       </c>
       <c r="D19" s="46" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="E19" s="46" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="F19" s="46" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="G19" s="47" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M01.01.06")</f>
@@ -4454,7 +4653,7 @@
       </c>
       <c r="H19" s="46"/>
       <c r="I19" s="46" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4470,7 +4669,7 @@
       <c r="D20" s="51"/>
       <c r="E20" s="51"/>
       <c r="F20" s="51" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="G20" s="52" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$B:$B,"M02")</f>
@@ -4481,7 +4680,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="44" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="B21" s="44" t="s">
         <v>22</v>
@@ -4490,11 +4689,11 @@
         <v>12</v>
       </c>
       <c r="D21" s="44" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="E21" s="44"/>
       <c r="F21" s="44" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="G21" s="45" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$D:$D,"M02.01")</f>
@@ -4505,7 +4704,7 @@
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="46" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B22" s="46" t="s">
         <v>23</v>
@@ -4514,13 +4713,13 @@
         <v>12</v>
       </c>
       <c r="D22" s="46" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="E22" s="46" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="F22" s="46" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="G22" s="47" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M02.01.01")</f>
@@ -4533,7 +4732,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="46" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="B23" s="46" t="s">
         <v>23</v>
@@ -4542,13 +4741,13 @@
         <v>12</v>
       </c>
       <c r="D23" s="46" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="E23" s="46" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F23" s="46" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="G23" s="47" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M02.01.02")</f>
@@ -4561,7 +4760,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="46" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="B24" s="46" t="s">
         <v>23</v>
@@ -4570,13 +4769,13 @@
         <v>12</v>
       </c>
       <c r="D24" s="46" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="E24" s="46" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="F24" s="46" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="G24" s="47" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M02.01.03")</f>
@@ -4589,7 +4788,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="46" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="B25" s="46" t="s">
         <v>23</v>
@@ -4598,13 +4797,13 @@
         <v>12</v>
       </c>
       <c r="D25" s="46" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="E25" s="46" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="F25" s="46" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="G25" s="47" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M02.01.04")</f>
@@ -4617,7 +4816,7 @@
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="46" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="B26" s="46" t="s">
         <v>23</v>
@@ -4626,13 +4825,13 @@
         <v>12</v>
       </c>
       <c r="D26" s="46" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="E26" s="46" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="F26" s="46" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="G26" s="47" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M02.01.05")</f>
@@ -4640,12 +4839,12 @@
       </c>
       <c r="H26" s="46"/>
       <c r="I26" s="46" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="46" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="B27" s="46" t="s">
         <v>23</v>
@@ -4654,13 +4853,13 @@
         <v>12</v>
       </c>
       <c r="D27" s="46" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="E27" s="46" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="F27" s="46" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="G27" s="47" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M02.01.06")</f>
@@ -4668,12 +4867,12 @@
       </c>
       <c r="H27" s="46"/>
       <c r="I27" s="46" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="44" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B28" s="44" t="s">
         <v>22</v>
@@ -4682,11 +4881,11 @@
         <v>12</v>
       </c>
       <c r="D28" s="44" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="E28" s="44"/>
       <c r="F28" s="44" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="G28" s="45" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$D:$D,"M02.02")</f>
@@ -4697,7 +4896,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="46" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="B29" s="46" t="s">
         <v>23</v>
@@ -4706,13 +4905,13 @@
         <v>12</v>
       </c>
       <c r="D29" s="46" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="E29" s="46" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="F29" s="46" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="G29" s="47" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M02.02.01")</f>
@@ -4725,7 +4924,7 @@
     </row>
     <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="46" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="B30" s="46" t="s">
         <v>23</v>
@@ -4734,13 +4933,13 @@
         <v>12</v>
       </c>
       <c r="D30" s="46" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="E30" s="46" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="F30" s="46" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="G30" s="47" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M02.02.02")</f>
@@ -4753,7 +4952,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="46" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B31" s="46" t="s">
         <v>23</v>
@@ -4762,13 +4961,13 @@
         <v>12</v>
       </c>
       <c r="D31" s="46" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="E31" s="46" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="F31" s="46" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="G31" s="47" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M02.02.03")</f>
@@ -4781,7 +4980,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="46" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="B32" s="46" t="s">
         <v>23</v>
@@ -4790,13 +4989,13 @@
         <v>12</v>
       </c>
       <c r="D32" s="46" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="E32" s="46" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F32" s="46" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="G32" s="47" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M02.02.04")</f>
@@ -4809,7 +5008,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="46" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="B33" s="46" t="s">
         <v>23</v>
@@ -4818,13 +5017,13 @@
         <v>12</v>
       </c>
       <c r="D33" s="46" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="E33" s="46" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="F33" s="46" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="G33" s="47" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M02.02.05")</f>
@@ -4837,7 +5036,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="46" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="B34" s="46" t="s">
         <v>23</v>
@@ -4846,13 +5045,13 @@
         <v>12</v>
       </c>
       <c r="D34" s="46" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="E34" s="46" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="F34" s="46" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="G34" s="47" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M02.02.06")</f>
@@ -4865,7 +5064,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="46" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="B35" s="46" t="s">
         <v>23</v>
@@ -4874,13 +5073,13 @@
         <v>12</v>
       </c>
       <c r="D35" s="46" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="E35" s="46" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="F35" s="46" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="G35" s="47" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M02.02.07")</f>
@@ -4893,7 +5092,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="44" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="B36" s="44" t="s">
         <v>22</v>
@@ -4902,11 +5101,11 @@
         <v>12</v>
       </c>
       <c r="D36" s="44" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="E36" s="44"/>
       <c r="F36" s="44" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="G36" s="45" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$D:$D,"M02.03")</f>
@@ -4917,7 +5116,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="46" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="B37" s="46" t="s">
         <v>23</v>
@@ -4926,13 +5125,13 @@
         <v>12</v>
       </c>
       <c r="D37" s="46" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="E37" s="46" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="F37" s="46" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="G37" s="47" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M02.03.01")</f>
@@ -4945,7 +5144,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="46" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="B38" s="46" t="s">
         <v>23</v>
@@ -4954,13 +5153,13 @@
         <v>12</v>
       </c>
       <c r="D38" s="46" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="E38" s="46" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="F38" s="46" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="G38" s="47" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M02.03.02")</f>
@@ -4973,7 +5172,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="46" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="B39" s="46" t="s">
         <v>23</v>
@@ -4982,13 +5181,13 @@
         <v>12</v>
       </c>
       <c r="D39" s="46" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="E39" s="46" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="F39" s="46" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="G39" s="47" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M02.03.03")</f>
@@ -5001,7 +5200,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="46" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="B40" s="46" t="s">
         <v>23</v>
@@ -5010,13 +5209,13 @@
         <v>12</v>
       </c>
       <c r="D40" s="46" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="E40" s="46" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="F40" s="46" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="G40" s="47" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M02.03.04")</f>
@@ -5029,7 +5228,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="46" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="B41" s="46" t="s">
         <v>23</v>
@@ -5038,13 +5237,13 @@
         <v>12</v>
       </c>
       <c r="D41" s="46" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="E41" s="46" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="F41" s="46" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="G41" s="47" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M02.03.05")</f>
@@ -5057,7 +5256,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="44" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="B42" s="44" t="s">
         <v>22</v>
@@ -5066,11 +5265,11 @@
         <v>12</v>
       </c>
       <c r="D42" s="44" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="E42" s="44"/>
       <c r="F42" s="44" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="G42" s="45" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$D:$D,"M02.04")</f>
@@ -5081,7 +5280,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="46" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="B43" s="46" t="s">
         <v>23</v>
@@ -5090,13 +5289,13 @@
         <v>12</v>
       </c>
       <c r="D43" s="46" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="E43" s="46" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="F43" s="46" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="G43" s="47" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M02.04.01")</f>
@@ -5109,7 +5308,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="46" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="B44" s="46" t="s">
         <v>23</v>
@@ -5118,13 +5317,13 @@
         <v>12</v>
       </c>
       <c r="D44" s="46" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="E44" s="46" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="F44" s="46" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="G44" s="47" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M02.04.02")</f>
@@ -5148,18 +5347,18 @@
       <c r="D45" s="53"/>
       <c r="E45" s="53"/>
       <c r="F45" s="53" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="G45" s="54" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$B:$B,"M03")</f>
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="H45" s="53"/>
       <c r="I45" s="53"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="44" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="B46" s="44" t="s">
         <v>22</v>
@@ -5168,11 +5367,11 @@
         <v>14</v>
       </c>
       <c r="D46" s="44" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="E46" s="44"/>
       <c r="F46" s="44" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="G46" s="45" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$D:$D,"M03.01")</f>
@@ -5183,7 +5382,7 @@
     </row>
     <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="46" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B47" s="46" t="s">
         <v>23</v>
@@ -5192,13 +5391,13 @@
         <v>14</v>
       </c>
       <c r="D47" s="46" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="E47" s="46" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="F47" s="46" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="G47" s="47" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.01.01")</f>
@@ -5211,7 +5410,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="44" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="B48" s="44" t="s">
         <v>22</v>
@@ -5220,11 +5419,11 @@
         <v>14</v>
       </c>
       <c r="D48" s="44" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="E48" s="44"/>
       <c r="F48" s="44" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="G48" s="45" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$D:$D,"M03.02")</f>
@@ -5235,7 +5434,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="46" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="B49" s="46" t="s">
         <v>23</v>
@@ -5244,13 +5443,13 @@
         <v>14</v>
       </c>
       <c r="D49" s="46" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="E49" s="46" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="F49" s="46" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="G49" s="47" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.02.01")</f>
@@ -5263,7 +5462,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="46" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="B50" s="46" t="s">
         <v>23</v>
@@ -5272,13 +5471,13 @@
         <v>14</v>
       </c>
       <c r="D50" s="46" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="E50" s="46" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="F50" s="46" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="G50" s="47" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.02.02")</f>
@@ -5291,7 +5490,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="46" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="B51" s="46" t="s">
         <v>23</v>
@@ -5300,13 +5499,13 @@
         <v>14</v>
       </c>
       <c r="D51" s="46" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="E51" s="46" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="F51" s="46" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="G51" s="47" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.02.03")</f>
@@ -5319,7 +5518,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="46" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="B52" s="46" t="s">
         <v>23</v>
@@ -5328,13 +5527,13 @@
         <v>14</v>
       </c>
       <c r="D52" s="46" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="E52" s="46" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="F52" s="46" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="G52" s="47" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.02.04")</f>
@@ -5347,7 +5546,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="46" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="B53" s="46" t="s">
         <v>23</v>
@@ -5356,13 +5555,13 @@
         <v>14</v>
       </c>
       <c r="D53" s="46" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="E53" s="46" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="F53" s="46" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="G53" s="47" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.02.05")</f>
@@ -5375,7 +5574,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="44" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="B54" s="44" t="s">
         <v>22</v>
@@ -5384,11 +5583,11 @@
         <v>14</v>
       </c>
       <c r="D54" s="44" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="E54" s="44"/>
       <c r="F54" s="44" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="G54" s="45" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$D:$D,"M03.03")</f>
@@ -5399,7 +5598,7 @@
     </row>
     <row r="55" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="46" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="B55" s="46" t="s">
         <v>23</v>
@@ -5408,13 +5607,13 @@
         <v>14</v>
       </c>
       <c r="D55" s="46" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="E55" s="46" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="F55" s="46" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="G55" s="47" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.03.01")</f>
@@ -5422,12 +5621,12 @@
       </c>
       <c r="H55" s="46"/>
       <c r="I55" s="46" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="46" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="B56" s="46" t="s">
         <v>23</v>
@@ -5436,13 +5635,13 @@
         <v>14</v>
       </c>
       <c r="D56" s="46" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="E56" s="46" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="F56" s="46" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="G56" s="47" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.03.02")</f>
@@ -5450,12 +5649,12 @@
       </c>
       <c r="H56" s="46"/>
       <c r="I56" s="46" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="46" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="B57" s="46" t="s">
         <v>23</v>
@@ -5464,13 +5663,13 @@
         <v>14</v>
       </c>
       <c r="D57" s="46" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="E57" s="46" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="F57" s="46" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="G57" s="47" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.03.03")</f>
@@ -5478,12 +5677,12 @@
       </c>
       <c r="H57" s="46"/>
       <c r="I57" s="46" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="46" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="B58" s="46" t="s">
         <v>23</v>
@@ -5492,13 +5691,13 @@
         <v>14</v>
       </c>
       <c r="D58" s="46" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="E58" s="46" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="F58" s="46" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="G58" s="47" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.03.04")</f>
@@ -5506,12 +5705,12 @@
       </c>
       <c r="H58" s="46"/>
       <c r="I58" s="46" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="44" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="B59" s="44" t="s">
         <v>22</v>
@@ -5520,11 +5719,11 @@
         <v>14</v>
       </c>
       <c r="D59" s="44" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="E59" s="44"/>
       <c r="F59" s="44" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="G59" s="45" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$D:$D,"M03.04")</f>
@@ -5535,7 +5734,7 @@
     </row>
     <row r="60" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="46" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="B60" s="46" t="s">
         <v>23</v>
@@ -5544,13 +5743,13 @@
         <v>14</v>
       </c>
       <c r="D60" s="46" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="E60" s="46" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="F60" s="46" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="G60" s="47" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.04.01")</f>
@@ -5563,7 +5762,7 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="46" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="B61" s="46" t="s">
         <v>23</v>
@@ -5572,13 +5771,13 @@
         <v>14</v>
       </c>
       <c r="D61" s="46" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="E61" s="46" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="F61" s="46" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="G61" s="47" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.04.02")</f>
@@ -5591,7 +5790,7 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="44" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="B62" s="44" t="s">
         <v>22</v>
@@ -5600,11 +5799,11 @@
         <v>14</v>
       </c>
       <c r="D62" s="44" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="E62" s="44"/>
       <c r="F62" s="44" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="G62" s="45" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$D:$D,"M03.05")</f>
@@ -5615,7 +5814,7 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="46" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="B63" s="46" t="s">
         <v>23</v>
@@ -5624,13 +5823,13 @@
         <v>14</v>
       </c>
       <c r="D63" s="46" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="E63" s="46" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="F63" s="46" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="G63" s="47" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.05.01")</f>
@@ -5643,7 +5842,7 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="46" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="B64" s="46" t="s">
         <v>23</v>
@@ -5652,13 +5851,13 @@
         <v>14</v>
       </c>
       <c r="D64" s="46" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="E64" s="46" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="F64" s="46" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="G64" s="47" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.05.02")</f>
@@ -5671,7 +5870,7 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="44" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="B65" s="44" t="s">
         <v>22</v>
@@ -5680,11 +5879,11 @@
         <v>14</v>
       </c>
       <c r="D65" s="44" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="E65" s="44"/>
       <c r="F65" s="44" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="G65" s="45" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$D:$D,"M03.06")</f>
@@ -5695,7 +5894,7 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="46" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="B66" s="46" t="s">
         <v>23</v>
@@ -5704,13 +5903,13 @@
         <v>14</v>
       </c>
       <c r="D66" s="46" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="E66" s="46" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="F66" s="46" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="G66" s="47" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.06.01")</f>
@@ -5723,7 +5922,7 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="46" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="B67" s="46" t="s">
         <v>23</v>
@@ -5732,13 +5931,13 @@
         <v>14</v>
       </c>
       <c r="D67" s="46" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="E67" s="46" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="F67" s="46" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="G67" s="47" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.06.02")</f>
@@ -5751,7 +5950,7 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="46" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="B68" s="46" t="s">
         <v>23</v>
@@ -5760,13 +5959,13 @@
         <v>14</v>
       </c>
       <c r="D68" s="46" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="E68" s="46" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="F68" s="46" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="G68" s="47" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.06.03")</f>
@@ -5779,7 +5978,7 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="44" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="B69" s="44" t="s">
         <v>22</v>
@@ -5788,22 +5987,22 @@
         <v>14</v>
       </c>
       <c r="D69" s="44" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="E69" s="44"/>
       <c r="F69" s="44" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="G69" s="45" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$D:$D,"M03.07")</f>
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H69" s="44"/>
       <c r="I69" s="44"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="46" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="B70" s="46" t="s">
         <v>23</v>
@@ -5812,13 +6011,13 @@
         <v>14</v>
       </c>
       <c r="D70" s="46" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="E70" s="46" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="F70" s="46" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="G70" s="47" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.07.01")</f>
@@ -5831,7 +6030,7 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="46" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="B71" s="46" t="s">
         <v>23</v>
@@ -5840,13 +6039,13 @@
         <v>14</v>
       </c>
       <c r="D71" s="46" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="E71" s="46" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="F71" s="46" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="G71" s="47" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.07.02")</f>
@@ -5857,9 +6056,9 @@
       </c>
       <c r="I71" s="46"/>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="46" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="B72" s="46" t="s">
         <v>23</v>
@@ -5868,17 +6067,17 @@
         <v>14</v>
       </c>
       <c r="D72" s="46" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="E72" s="46" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="F72" s="46" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="G72" s="47" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.07.03")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H72" s="50" t="s">
         <v>35</v>
@@ -5886,32 +6085,36 @@
       <c r="I72" s="46"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="44" t="s">
-        <v>340</v>
-      </c>
-      <c r="B73" s="44" t="s">
-        <v>22</v>
-      </c>
-      <c r="C73" s="44" t="s">
+      <c r="A73" s="46" t="s">
+        <v>345</v>
+      </c>
+      <c r="B73" s="46" t="s">
+        <v>23</v>
+      </c>
+      <c r="C73" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="D73" s="44" t="s">
-        <v>341</v>
-      </c>
-      <c r="E73" s="44"/>
-      <c r="F73" s="44" t="s">
-        <v>342</v>
-      </c>
-      <c r="G73" s="45" t="n">
-        <f aca="false">COUNTIF('Screen Inventory'!$D:$D,"M03.08")</f>
-        <v>1</v>
-      </c>
-      <c r="H73" s="44"/>
-      <c r="I73" s="44"/>
+      <c r="D73" s="46" t="s">
+        <v>334</v>
+      </c>
+      <c r="E73" s="46" t="s">
+        <v>346</v>
+      </c>
+      <c r="F73" s="46" t="s">
+        <v>347</v>
+      </c>
+      <c r="G73" s="47" t="n">
+        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.07.04")</f>
+        <v>1</v>
+      </c>
+      <c r="H73" s="50" t="s">
+        <v>35</v>
+      </c>
+      <c r="I73" s="46"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="46" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="B74" s="46" t="s">
         <v>23</v>
@@ -5920,190 +6123,186 @@
         <v>14</v>
       </c>
       <c r="D74" s="46" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="E74" s="46" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="F74" s="46" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="G74" s="47" t="n">
+        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.07.05")</f>
+        <v>1</v>
+      </c>
+      <c r="H74" s="50" t="s">
+        <v>35</v>
+      </c>
+      <c r="I74" s="46"/>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="46" t="s">
+        <v>351</v>
+      </c>
+      <c r="B75" s="46" t="s">
+        <v>23</v>
+      </c>
+      <c r="C75" s="46" t="s">
+        <v>14</v>
+      </c>
+      <c r="D75" s="46" t="s">
+        <v>334</v>
+      </c>
+      <c r="E75" s="46" t="s">
+        <v>352</v>
+      </c>
+      <c r="F75" s="46" t="s">
+        <v>353</v>
+      </c>
+      <c r="G75" s="47" t="n">
+        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.07.06")</f>
+        <v>1</v>
+      </c>
+      <c r="H75" s="50" t="s">
+        <v>35</v>
+      </c>
+      <c r="I75" s="46"/>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="46" t="s">
+        <v>354</v>
+      </c>
+      <c r="B76" s="46" t="s">
+        <v>23</v>
+      </c>
+      <c r="C76" s="46" t="s">
+        <v>14</v>
+      </c>
+      <c r="D76" s="46" t="s">
+        <v>334</v>
+      </c>
+      <c r="E76" s="46" t="s">
+        <v>355</v>
+      </c>
+      <c r="F76" s="46" t="s">
+        <v>356</v>
+      </c>
+      <c r="G76" s="47" t="n">
+        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.07.07")</f>
+        <v>1</v>
+      </c>
+      <c r="H76" s="50" t="s">
+        <v>35</v>
+      </c>
+      <c r="I76" s="46"/>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="46" t="s">
+        <v>357</v>
+      </c>
+      <c r="B77" s="46" t="s">
+        <v>23</v>
+      </c>
+      <c r="C77" s="46" t="s">
+        <v>14</v>
+      </c>
+      <c r="D77" s="46" t="s">
+        <v>334</v>
+      </c>
+      <c r="E77" s="46" t="s">
+        <v>358</v>
+      </c>
+      <c r="F77" s="46" t="s">
+        <v>359</v>
+      </c>
+      <c r="G77" s="47" t="n">
+        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.07.08")</f>
+        <v>1</v>
+      </c>
+      <c r="H77" s="50" t="s">
+        <v>35</v>
+      </c>
+      <c r="I77" s="46"/>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="44" t="s">
+        <v>360</v>
+      </c>
+      <c r="B78" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="C78" s="44" t="s">
+        <v>14</v>
+      </c>
+      <c r="D78" s="44" t="s">
+        <v>361</v>
+      </c>
+      <c r="E78" s="44"/>
+      <c r="F78" s="44" t="s">
+        <v>362</v>
+      </c>
+      <c r="G78" s="45" t="n">
+        <f aca="false">COUNTIF('Screen Inventory'!$D:$D,"M03.08")</f>
+        <v>1</v>
+      </c>
+      <c r="H78" s="44"/>
+      <c r="I78" s="44"/>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="46" t="s">
+        <v>363</v>
+      </c>
+      <c r="B79" s="46" t="s">
+        <v>23</v>
+      </c>
+      <c r="C79" s="46" t="s">
+        <v>14</v>
+      </c>
+      <c r="D79" s="46" t="s">
+        <v>361</v>
+      </c>
+      <c r="E79" s="46" t="s">
+        <v>364</v>
+      </c>
+      <c r="F79" s="46" t="s">
+        <v>365</v>
+      </c>
+      <c r="G79" s="47" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.08.01")</f>
         <v>1</v>
       </c>
-      <c r="H74" s="50" t="s">
-        <v>35</v>
-      </c>
-      <c r="I74" s="46"/>
-    </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="44" t="s">
-        <v>346</v>
-      </c>
-      <c r="B75" s="44" t="s">
+      <c r="H79" s="50" t="s">
+        <v>35</v>
+      </c>
+      <c r="I79" s="46"/>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="44" t="s">
+        <v>366</v>
+      </c>
+      <c r="B80" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="C75" s="44" t="s">
+      <c r="C80" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="D75" s="44" t="s">
-        <v>347</v>
-      </c>
-      <c r="E75" s="44"/>
-      <c r="F75" s="44" t="s">
-        <v>348</v>
-      </c>
-      <c r="G75" s="45" t="n">
+      <c r="D80" s="44" t="s">
+        <v>367</v>
+      </c>
+      <c r="E80" s="44"/>
+      <c r="F80" s="44" t="s">
+        <v>368</v>
+      </c>
+      <c r="G80" s="45" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$D:$D,"M03.09")</f>
         <v>11</v>
       </c>
-      <c r="H75" s="44"/>
-      <c r="I75" s="44"/>
-    </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="46" t="s">
-        <v>349</v>
-      </c>
-      <c r="B76" s="46" t="s">
-        <v>23</v>
-      </c>
-      <c r="C76" s="46" t="s">
-        <v>14</v>
-      </c>
-      <c r="D76" s="46" t="s">
-        <v>347</v>
-      </c>
-      <c r="E76" s="46" t="s">
-        <v>350</v>
-      </c>
-      <c r="F76" s="46" t="s">
-        <v>351</v>
-      </c>
-      <c r="G76" s="47" t="n">
-        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.09.01")</f>
-        <v>1</v>
-      </c>
-      <c r="H76" s="50" t="s">
-        <v>35</v>
-      </c>
-      <c r="I76" s="46"/>
-    </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="46" t="s">
-        <v>352</v>
-      </c>
-      <c r="B77" s="46" t="s">
-        <v>23</v>
-      </c>
-      <c r="C77" s="46" t="s">
-        <v>14</v>
-      </c>
-      <c r="D77" s="46" t="s">
-        <v>347</v>
-      </c>
-      <c r="E77" s="46" t="s">
-        <v>353</v>
-      </c>
-      <c r="F77" s="46" t="s">
-        <v>354</v>
-      </c>
-      <c r="G77" s="47" t="n">
-        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.09.02")</f>
-        <v>1</v>
-      </c>
-      <c r="H77" s="50" t="s">
-        <v>35</v>
-      </c>
-      <c r="I77" s="46"/>
-    </row>
-    <row r="78" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="46" t="s">
-        <v>355</v>
-      </c>
-      <c r="B78" s="46" t="s">
-        <v>23</v>
-      </c>
-      <c r="C78" s="46" t="s">
-        <v>14</v>
-      </c>
-      <c r="D78" s="46" t="s">
-        <v>347</v>
-      </c>
-      <c r="E78" s="46" t="s">
-        <v>356</v>
-      </c>
-      <c r="F78" s="46" t="s">
-        <v>357</v>
-      </c>
-      <c r="G78" s="47" t="n">
-        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.09.03")</f>
-        <v>1</v>
-      </c>
-      <c r="H78" s="50" t="s">
-        <v>35</v>
-      </c>
-      <c r="I78" s="46"/>
-    </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="46" t="s">
-        <v>358</v>
-      </c>
-      <c r="B79" s="46" t="s">
-        <v>23</v>
-      </c>
-      <c r="C79" s="46" t="s">
-        <v>14</v>
-      </c>
-      <c r="D79" s="46" t="s">
-        <v>347</v>
-      </c>
-      <c r="E79" s="46" t="s">
-        <v>359</v>
-      </c>
-      <c r="F79" s="46" t="s">
-        <v>360</v>
-      </c>
-      <c r="G79" s="47" t="n">
-        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.09.04")</f>
-        <v>1</v>
-      </c>
-      <c r="H79" s="50" t="s">
-        <v>35</v>
-      </c>
-      <c r="I79" s="46"/>
-    </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="46" t="s">
-        <v>361</v>
-      </c>
-      <c r="B80" s="46" t="s">
-        <v>23</v>
-      </c>
-      <c r="C80" s="46" t="s">
-        <v>14</v>
-      </c>
-      <c r="D80" s="46" t="s">
-        <v>347</v>
-      </c>
-      <c r="E80" s="46" t="s">
-        <v>362</v>
-      </c>
-      <c r="F80" s="46" t="s">
-        <v>363</v>
-      </c>
-      <c r="G80" s="47" t="n">
-        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.09.05")</f>
-        <v>1</v>
-      </c>
-      <c r="H80" s="50" t="s">
-        <v>35</v>
-      </c>
-      <c r="I80" s="46"/>
+      <c r="H80" s="44"/>
+      <c r="I80" s="44"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="46" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="B81" s="46" t="s">
         <v>23</v>
@@ -6112,16 +6311,16 @@
         <v>14</v>
       </c>
       <c r="D81" s="46" t="s">
-        <v>347</v>
+        <v>367</v>
       </c>
       <c r="E81" s="46" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="F81" s="46" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="G81" s="47" t="n">
-        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.09.06")</f>
+        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.09.01")</f>
         <v>1</v>
       </c>
       <c r="H81" s="50" t="s">
@@ -6131,7 +6330,7 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="46" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="B82" s="46" t="s">
         <v>23</v>
@@ -6140,456 +6339,460 @@
         <v>14</v>
       </c>
       <c r="D82" s="46" t="s">
-        <v>347</v>
+        <v>367</v>
       </c>
       <c r="E82" s="46" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="F82" s="46" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="G82" s="47" t="n">
+        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.09.02")</f>
+        <v>1</v>
+      </c>
+      <c r="H82" s="50" t="s">
+        <v>35</v>
+      </c>
+      <c r="I82" s="46"/>
+    </row>
+    <row r="83" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="46" t="s">
+        <v>375</v>
+      </c>
+      <c r="B83" s="46" t="s">
+        <v>23</v>
+      </c>
+      <c r="C83" s="46" t="s">
+        <v>14</v>
+      </c>
+      <c r="D83" s="46" t="s">
+        <v>367</v>
+      </c>
+      <c r="E83" s="46" t="s">
+        <v>376</v>
+      </c>
+      <c r="F83" s="46" t="s">
+        <v>377</v>
+      </c>
+      <c r="G83" s="47" t="n">
+        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.09.03")</f>
+        <v>1</v>
+      </c>
+      <c r="H83" s="50" t="s">
+        <v>35</v>
+      </c>
+      <c r="I83" s="46"/>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="46" t="s">
+        <v>378</v>
+      </c>
+      <c r="B84" s="46" t="s">
+        <v>23</v>
+      </c>
+      <c r="C84" s="46" t="s">
+        <v>14</v>
+      </c>
+      <c r="D84" s="46" t="s">
+        <v>367</v>
+      </c>
+      <c r="E84" s="46" t="s">
+        <v>379</v>
+      </c>
+      <c r="F84" s="46" t="s">
+        <v>380</v>
+      </c>
+      <c r="G84" s="47" t="n">
+        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.09.04")</f>
+        <v>1</v>
+      </c>
+      <c r="H84" s="50" t="s">
+        <v>35</v>
+      </c>
+      <c r="I84" s="46"/>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="46" t="s">
+        <v>381</v>
+      </c>
+      <c r="B85" s="46" t="s">
+        <v>23</v>
+      </c>
+      <c r="C85" s="46" t="s">
+        <v>14</v>
+      </c>
+      <c r="D85" s="46" t="s">
+        <v>367</v>
+      </c>
+      <c r="E85" s="46" t="s">
+        <v>382</v>
+      </c>
+      <c r="F85" s="46" t="s">
+        <v>383</v>
+      </c>
+      <c r="G85" s="47" t="n">
+        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.09.05")</f>
+        <v>1</v>
+      </c>
+      <c r="H85" s="50" t="s">
+        <v>35</v>
+      </c>
+      <c r="I85" s="46"/>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="46" t="s">
+        <v>384</v>
+      </c>
+      <c r="B86" s="46" t="s">
+        <v>23</v>
+      </c>
+      <c r="C86" s="46" t="s">
+        <v>14</v>
+      </c>
+      <c r="D86" s="46" t="s">
+        <v>367</v>
+      </c>
+      <c r="E86" s="46" t="s">
+        <v>385</v>
+      </c>
+      <c r="F86" s="46" t="s">
+        <v>386</v>
+      </c>
+      <c r="G86" s="47" t="n">
+        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.09.06")</f>
+        <v>1</v>
+      </c>
+      <c r="H86" s="50" t="s">
+        <v>35</v>
+      </c>
+      <c r="I86" s="46"/>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="46" t="s">
+        <v>387</v>
+      </c>
+      <c r="B87" s="46" t="s">
+        <v>23</v>
+      </c>
+      <c r="C87" s="46" t="s">
+        <v>14</v>
+      </c>
+      <c r="D87" s="46" t="s">
+        <v>367</v>
+      </c>
+      <c r="E87" s="46" t="s">
+        <v>388</v>
+      </c>
+      <c r="F87" s="46" t="s">
+        <v>389</v>
+      </c>
+      <c r="G87" s="47" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.09.07")</f>
         <v>3</v>
       </c>
-      <c r="H82" s="50" t="s">
-        <v>35</v>
-      </c>
-      <c r="I82" s="46"/>
-    </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="46" t="s">
-        <v>370</v>
-      </c>
-      <c r="B83" s="46" t="s">
+      <c r="H87" s="50" t="s">
+        <v>35</v>
+      </c>
+      <c r="I87" s="46"/>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="46" t="s">
+        <v>390</v>
+      </c>
+      <c r="B88" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="C83" s="46" t="s">
+      <c r="C88" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="D83" s="46" t="s">
-        <v>347</v>
-      </c>
-      <c r="E83" s="46" t="s">
-        <v>371</v>
-      </c>
-      <c r="F83" s="46" t="s">
-        <v>372</v>
-      </c>
-      <c r="G83" s="47" t="n">
+      <c r="D88" s="46" t="s">
+        <v>367</v>
+      </c>
+      <c r="E88" s="46" t="s">
+        <v>391</v>
+      </c>
+      <c r="F88" s="46" t="s">
+        <v>392</v>
+      </c>
+      <c r="G88" s="47" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.09.08")</f>
         <v>1</v>
       </c>
-      <c r="H83" s="50" t="s">
-        <v>35</v>
-      </c>
-      <c r="I83" s="46"/>
-    </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="46" t="s">
-        <v>373</v>
-      </c>
-      <c r="B84" s="46" t="s">
+      <c r="H88" s="50" t="s">
+        <v>35</v>
+      </c>
+      <c r="I88" s="46"/>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="46" t="s">
+        <v>393</v>
+      </c>
+      <c r="B89" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="C84" s="46" t="s">
+      <c r="C89" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="D84" s="46" t="s">
-        <v>347</v>
-      </c>
-      <c r="E84" s="46" t="s">
-        <v>374</v>
-      </c>
-      <c r="F84" s="46" t="s">
-        <v>375</v>
-      </c>
-      <c r="G84" s="47" t="n">
+      <c r="D89" s="46" t="s">
+        <v>367</v>
+      </c>
+      <c r="E89" s="46" t="s">
+        <v>394</v>
+      </c>
+      <c r="F89" s="46" t="s">
+        <v>395</v>
+      </c>
+      <c r="G89" s="47" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.09.09")</f>
         <v>1</v>
       </c>
-      <c r="H84" s="50" t="s">
-        <v>35</v>
-      </c>
-      <c r="I84" s="46"/>
-    </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="44" t="s">
-        <v>376</v>
-      </c>
-      <c r="B85" s="44" t="s">
+      <c r="H89" s="50" t="s">
+        <v>35</v>
+      </c>
+      <c r="I89" s="46"/>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="44" t="s">
+        <v>396</v>
+      </c>
+      <c r="B90" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="C85" s="44" t="s">
+      <c r="C90" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="D85" s="44" t="s">
-        <v>377</v>
-      </c>
-      <c r="E85" s="44"/>
-      <c r="F85" s="44" t="s">
-        <v>378</v>
-      </c>
-      <c r="G85" s="45" t="n">
+      <c r="D90" s="44" t="s">
+        <v>397</v>
+      </c>
+      <c r="E90" s="44"/>
+      <c r="F90" s="44" t="s">
+        <v>398</v>
+      </c>
+      <c r="G90" s="45" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$D:$D,"M03.10")</f>
         <v>11</v>
       </c>
-      <c r="H85" s="44"/>
-      <c r="I85" s="44"/>
-    </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="46" t="s">
-        <v>379</v>
-      </c>
-      <c r="B86" s="46" t="s">
+      <c r="H90" s="44"/>
+      <c r="I90" s="44"/>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="46" t="s">
+        <v>399</v>
+      </c>
+      <c r="B91" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="C86" s="46" t="s">
+      <c r="C91" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="D86" s="46" t="s">
-        <v>377</v>
-      </c>
-      <c r="E86" s="46" t="s">
-        <v>380</v>
-      </c>
-      <c r="F86" s="46" t="s">
-        <v>381</v>
-      </c>
-      <c r="G86" s="47" t="n">
+      <c r="D91" s="46" t="s">
+        <v>397</v>
+      </c>
+      <c r="E91" s="46" t="s">
+        <v>400</v>
+      </c>
+      <c r="F91" s="46" t="s">
+        <v>401</v>
+      </c>
+      <c r="G91" s="47" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.10.01")</f>
         <v>2</v>
       </c>
-      <c r="H86" s="50" t="s">
-        <v>35</v>
-      </c>
-      <c r="I86" s="46"/>
-    </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="46" t="s">
-        <v>382</v>
-      </c>
-      <c r="B87" s="46" t="s">
+      <c r="H91" s="50" t="s">
+        <v>35</v>
+      </c>
+      <c r="I91" s="46"/>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="46" t="s">
+        <v>402</v>
+      </c>
+      <c r="B92" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="C87" s="46" t="s">
+      <c r="C92" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="D87" s="46" t="s">
-        <v>377</v>
-      </c>
-      <c r="E87" s="46" t="s">
-        <v>383</v>
-      </c>
-      <c r="F87" s="46" t="s">
-        <v>384</v>
-      </c>
-      <c r="G87" s="47" t="n">
+      <c r="D92" s="46" t="s">
+        <v>397</v>
+      </c>
+      <c r="E92" s="46" t="s">
+        <v>403</v>
+      </c>
+      <c r="F92" s="46" t="s">
+        <v>404</v>
+      </c>
+      <c r="G92" s="47" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.10.02")</f>
         <v>2</v>
       </c>
-      <c r="H87" s="50" t="s">
-        <v>35</v>
-      </c>
-      <c r="I87" s="46"/>
-    </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="46" t="s">
-        <v>385</v>
-      </c>
-      <c r="B88" s="46" t="s">
+      <c r="H92" s="50" t="s">
+        <v>35</v>
+      </c>
+      <c r="I92" s="46"/>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="46" t="s">
+        <v>405</v>
+      </c>
+      <c r="B93" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="C88" s="46" t="s">
+      <c r="C93" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="D88" s="46" t="s">
-        <v>377</v>
-      </c>
-      <c r="E88" s="46" t="s">
-        <v>386</v>
-      </c>
-      <c r="F88" s="46" t="s">
-        <v>387</v>
-      </c>
-      <c r="G88" s="47" t="n">
+      <c r="D93" s="46" t="s">
+        <v>397</v>
+      </c>
+      <c r="E93" s="46" t="s">
+        <v>406</v>
+      </c>
+      <c r="F93" s="46" t="s">
+        <v>407</v>
+      </c>
+      <c r="G93" s="47" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.10.03")</f>
         <v>1</v>
       </c>
-      <c r="H88" s="50" t="s">
-        <v>35</v>
-      </c>
-      <c r="I88" s="46"/>
-    </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="46" t="s">
-        <v>388</v>
-      </c>
-      <c r="B89" s="46" t="s">
+      <c r="H93" s="50" t="s">
+        <v>35</v>
+      </c>
+      <c r="I93" s="46"/>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="46" t="s">
+        <v>408</v>
+      </c>
+      <c r="B94" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="C89" s="46" t="s">
+      <c r="C94" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="D89" s="46" t="s">
-        <v>377</v>
-      </c>
-      <c r="E89" s="46" t="s">
-        <v>389</v>
-      </c>
-      <c r="F89" s="46" t="s">
-        <v>390</v>
-      </c>
-      <c r="G89" s="47" t="n">
+      <c r="D94" s="46" t="s">
+        <v>397</v>
+      </c>
+      <c r="E94" s="46" t="s">
+        <v>409</v>
+      </c>
+      <c r="F94" s="46" t="s">
+        <v>410</v>
+      </c>
+      <c r="G94" s="47" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.10.04")</f>
         <v>3</v>
       </c>
-      <c r="H89" s="50" t="s">
-        <v>35</v>
-      </c>
-      <c r="I89" s="46"/>
-    </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="46" t="s">
-        <v>391</v>
-      </c>
-      <c r="B90" s="46" t="s">
+      <c r="H94" s="50" t="s">
+        <v>35</v>
+      </c>
+      <c r="I94" s="46"/>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="46" t="s">
+        <v>411</v>
+      </c>
+      <c r="B95" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="C90" s="46" t="s">
+      <c r="C95" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="D90" s="46" t="s">
-        <v>377</v>
-      </c>
-      <c r="E90" s="46" t="s">
-        <v>392</v>
-      </c>
-      <c r="F90" s="46" t="s">
-        <v>393</v>
-      </c>
-      <c r="G90" s="47" t="n">
+      <c r="D95" s="46" t="s">
+        <v>397</v>
+      </c>
+      <c r="E95" s="46" t="s">
+        <v>412</v>
+      </c>
+      <c r="F95" s="46" t="s">
+        <v>413</v>
+      </c>
+      <c r="G95" s="47" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M03.10.05")</f>
         <v>3</v>
       </c>
-      <c r="H90" s="50" t="s">
-        <v>35</v>
-      </c>
-      <c r="I90" s="46"/>
-    </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="55" t="s">
+      <c r="H95" s="50" t="s">
+        <v>35</v>
+      </c>
+      <c r="I95" s="46"/>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="55" t="s">
         <v>15</v>
       </c>
-      <c r="B91" s="55" t="s">
+      <c r="B96" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="C91" s="55" t="s">
+      <c r="C96" s="55" t="s">
         <v>16</v>
       </c>
-      <c r="D91" s="55"/>
-      <c r="E91" s="55"/>
-      <c r="F91" s="55" t="s">
-        <v>394</v>
-      </c>
-      <c r="G91" s="56" t="n">
+      <c r="D96" s="55"/>
+      <c r="E96" s="55"/>
+      <c r="F96" s="55" t="s">
+        <v>414</v>
+      </c>
+      <c r="G96" s="56" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$B:$B,"M04")</f>
         <v>6</v>
       </c>
-      <c r="H91" s="55"/>
-      <c r="I91" s="55"/>
-    </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="44" t="s">
-        <v>395</v>
-      </c>
-      <c r="B92" s="44" t="s">
+      <c r="H96" s="55"/>
+      <c r="I96" s="55"/>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="44" t="s">
+        <v>415</v>
+      </c>
+      <c r="B97" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="C92" s="44" t="s">
+      <c r="C97" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="D92" s="44" t="s">
-        <v>396</v>
-      </c>
-      <c r="E92" s="44"/>
-      <c r="F92" s="44" t="s">
-        <v>397</v>
-      </c>
-      <c r="G92" s="45" t="n">
+      <c r="D97" s="44" t="s">
+        <v>416</v>
+      </c>
+      <c r="E97" s="44"/>
+      <c r="F97" s="44" t="s">
+        <v>417</v>
+      </c>
+      <c r="G97" s="45" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$D:$D,"M04.01")</f>
         <v>5</v>
       </c>
-      <c r="H92" s="44"/>
-      <c r="I92" s="44"/>
-    </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="46" t="s">
-        <v>398</v>
-      </c>
-      <c r="B93" s="46" t="s">
+      <c r="H97" s="44"/>
+      <c r="I97" s="44"/>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="46" t="s">
+        <v>418</v>
+      </c>
+      <c r="B98" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="C93" s="46" t="s">
+      <c r="C98" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="D93" s="46" t="s">
-        <v>396</v>
-      </c>
-      <c r="E93" s="46" t="s">
-        <v>399</v>
-      </c>
-      <c r="F93" s="46" t="s">
-        <v>400</v>
-      </c>
-      <c r="G93" s="47" t="n">
+      <c r="D98" s="46" t="s">
+        <v>416</v>
+      </c>
+      <c r="E98" s="46" t="s">
+        <v>419</v>
+      </c>
+      <c r="F98" s="46" t="s">
+        <v>420</v>
+      </c>
+      <c r="G98" s="47" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M04.01.01")</f>
         <v>1</v>
       </c>
-      <c r="H93" s="50" t="s">
-        <v>35</v>
-      </c>
-      <c r="I93" s="46"/>
-    </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="46" t="s">
-        <v>401</v>
-      </c>
-      <c r="B94" s="46" t="s">
-        <v>23</v>
-      </c>
-      <c r="C94" s="46" t="s">
-        <v>16</v>
-      </c>
-      <c r="D94" s="46" t="s">
-        <v>396</v>
-      </c>
-      <c r="E94" s="46" t="s">
-        <v>402</v>
-      </c>
-      <c r="F94" s="46" t="s">
-        <v>403</v>
-      </c>
-      <c r="G94" s="47" t="n">
-        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M04.01.02")</f>
-        <v>1</v>
-      </c>
-      <c r="H94" s="50" t="s">
-        <v>35</v>
-      </c>
-      <c r="I94" s="46"/>
-    </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="46" t="s">
-        <v>404</v>
-      </c>
-      <c r="B95" s="46" t="s">
-        <v>23</v>
-      </c>
-      <c r="C95" s="46" t="s">
-        <v>16</v>
-      </c>
-      <c r="D95" s="46" t="s">
-        <v>396</v>
-      </c>
-      <c r="E95" s="46" t="s">
-        <v>405</v>
-      </c>
-      <c r="F95" s="46" t="s">
-        <v>406</v>
-      </c>
-      <c r="G95" s="47" t="n">
-        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M04.01.03")</f>
-        <v>1</v>
-      </c>
-      <c r="H95" s="50" t="s">
-        <v>35</v>
-      </c>
-      <c r="I95" s="46"/>
-    </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="46" t="s">
-        <v>407</v>
-      </c>
-      <c r="B96" s="46" t="s">
-        <v>23</v>
-      </c>
-      <c r="C96" s="46" t="s">
-        <v>16</v>
-      </c>
-      <c r="D96" s="46" t="s">
-        <v>396</v>
-      </c>
-      <c r="E96" s="46" t="s">
-        <v>408</v>
-      </c>
-      <c r="F96" s="46" t="s">
-        <v>409</v>
-      </c>
-      <c r="G96" s="47" t="n">
-        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M04.01.04")</f>
-        <v>1</v>
-      </c>
-      <c r="H96" s="50" t="s">
-        <v>35</v>
-      </c>
-      <c r="I96" s="46"/>
-    </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="46" t="s">
-        <v>410</v>
-      </c>
-      <c r="B97" s="46" t="s">
-        <v>23</v>
-      </c>
-      <c r="C97" s="46" t="s">
-        <v>16</v>
-      </c>
-      <c r="D97" s="46" t="s">
-        <v>396</v>
-      </c>
-      <c r="E97" s="46" t="s">
-        <v>411</v>
-      </c>
-      <c r="F97" s="46" t="s">
-        <v>412</v>
-      </c>
-      <c r="G97" s="47" t="n">
-        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M04.01.05")</f>
-        <v>1</v>
-      </c>
-      <c r="H97" s="50" t="s">
-        <v>35</v>
-      </c>
-      <c r="I97" s="46"/>
-    </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="44" t="s">
-        <v>413</v>
-      </c>
-      <c r="B98" s="44" t="s">
-        <v>22</v>
-      </c>
-      <c r="C98" s="44" t="s">
-        <v>16</v>
-      </c>
-      <c r="D98" s="44" t="s">
-        <v>414</v>
-      </c>
-      <c r="E98" s="44"/>
-      <c r="F98" s="44" t="s">
-        <v>415</v>
-      </c>
-      <c r="G98" s="45" t="n">
-        <f aca="false">COUNTIF('Screen Inventory'!$D:$D,"M04.02")</f>
-        <v>1</v>
-      </c>
-      <c r="H98" s="44"/>
-      <c r="I98" s="44"/>
-    </row>
-    <row r="99" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H98" s="50" t="s">
+        <v>35</v>
+      </c>
+      <c r="I98" s="46"/>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="46" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="B99" s="46" t="s">
         <v>23</v>
@@ -6598,212 +6801,208 @@
         <v>16</v>
       </c>
       <c r="D99" s="46" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E99" s="46" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="F99" s="46" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="G99" s="47" t="n">
+        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M04.01.02")</f>
+        <v>1</v>
+      </c>
+      <c r="H99" s="50" t="s">
+        <v>35</v>
+      </c>
+      <c r="I99" s="46"/>
+    </row>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="46" t="s">
+        <v>424</v>
+      </c>
+      <c r="B100" s="46" t="s">
+        <v>23</v>
+      </c>
+      <c r="C100" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="D100" s="46" t="s">
+        <v>416</v>
+      </c>
+      <c r="E100" s="46" t="s">
+        <v>425</v>
+      </c>
+      <c r="F100" s="46" t="s">
+        <v>426</v>
+      </c>
+      <c r="G100" s="47" t="n">
+        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M04.01.03")</f>
+        <v>1</v>
+      </c>
+      <c r="H100" s="50" t="s">
+        <v>35</v>
+      </c>
+      <c r="I100" s="46"/>
+    </row>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="46" t="s">
+        <v>427</v>
+      </c>
+      <c r="B101" s="46" t="s">
+        <v>23</v>
+      </c>
+      <c r="C101" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="D101" s="46" t="s">
+        <v>416</v>
+      </c>
+      <c r="E101" s="46" t="s">
+        <v>428</v>
+      </c>
+      <c r="F101" s="46" t="s">
+        <v>429</v>
+      </c>
+      <c r="G101" s="47" t="n">
+        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M04.01.04")</f>
+        <v>1</v>
+      </c>
+      <c r="H101" s="50" t="s">
+        <v>35</v>
+      </c>
+      <c r="I101" s="46"/>
+    </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="46" t="s">
+        <v>430</v>
+      </c>
+      <c r="B102" s="46" t="s">
+        <v>23</v>
+      </c>
+      <c r="C102" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="D102" s="46" t="s">
+        <v>416</v>
+      </c>
+      <c r="E102" s="46" t="s">
+        <v>431</v>
+      </c>
+      <c r="F102" s="46" t="s">
+        <v>432</v>
+      </c>
+      <c r="G102" s="47" t="n">
+        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M04.01.05")</f>
+        <v>1</v>
+      </c>
+      <c r="H102" s="50" t="s">
+        <v>35</v>
+      </c>
+      <c r="I102" s="46"/>
+    </row>
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="44" t="s">
+        <v>433</v>
+      </c>
+      <c r="B103" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="C103" s="44" t="s">
+        <v>16</v>
+      </c>
+      <c r="D103" s="44" t="s">
+        <v>434</v>
+      </c>
+      <c r="E103" s="44"/>
+      <c r="F103" s="44" t="s">
+        <v>435</v>
+      </c>
+      <c r="G103" s="45" t="n">
+        <f aca="false">COUNTIF('Screen Inventory'!$D:$D,"M04.02")</f>
+        <v>1</v>
+      </c>
+      <c r="H103" s="44"/>
+      <c r="I103" s="44"/>
+    </row>
+    <row r="104" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="46" t="s">
+        <v>436</v>
+      </c>
+      <c r="B104" s="46" t="s">
+        <v>23</v>
+      </c>
+      <c r="C104" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="D104" s="46" t="s">
+        <v>434</v>
+      </c>
+      <c r="E104" s="46" t="s">
+        <v>437</v>
+      </c>
+      <c r="F104" s="46" t="s">
+        <v>438</v>
+      </c>
+      <c r="G104" s="47" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M04.02.01")</f>
         <v>1</v>
       </c>
-      <c r="H99" s="50" t="s">
-        <v>35</v>
-      </c>
-      <c r="I99" s="46"/>
-    </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="57" t="s">
+      <c r="H104" s="50" t="s">
+        <v>35</v>
+      </c>
+      <c r="I104" s="46"/>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="B100" s="57" t="s">
+      <c r="B105" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="C100" s="57" t="s">
+      <c r="C105" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="D100" s="57"/>
-      <c r="E100" s="57"/>
-      <c r="F100" s="57" t="s">
-        <v>419</v>
-      </c>
-      <c r="G100" s="58" t="n">
+      <c r="D105" s="57"/>
+      <c r="E105" s="57"/>
+      <c r="F105" s="57" t="s">
+        <v>439</v>
+      </c>
+      <c r="G105" s="58" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$B:$B,"M05")</f>
         <v>11</v>
       </c>
-      <c r="H100" s="57"/>
-      <c r="I100" s="57"/>
-    </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="44" t="s">
-        <v>420</v>
-      </c>
-      <c r="B101" s="44" t="s">
+      <c r="H105" s="57"/>
+      <c r="I105" s="57"/>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="44" t="s">
+        <v>440</v>
+      </c>
+      <c r="B106" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="C101" s="44" t="s">
+      <c r="C106" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="D101" s="44" t="s">
-        <v>421</v>
-      </c>
-      <c r="E101" s="44"/>
-      <c r="F101" s="44" t="s">
-        <v>422</v>
-      </c>
-      <c r="G101" s="45" t="n">
+      <c r="D106" s="44" t="s">
+        <v>441</v>
+      </c>
+      <c r="E106" s="44"/>
+      <c r="F106" s="44" t="s">
+        <v>442</v>
+      </c>
+      <c r="G106" s="45" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$D:$D,"M05.01")</f>
         <v>6</v>
       </c>
-      <c r="H101" s="44"/>
-      <c r="I101" s="44"/>
-    </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="46" t="s">
-        <v>423</v>
-      </c>
-      <c r="B102" s="46" t="s">
-        <v>23</v>
-      </c>
-      <c r="C102" s="46" t="s">
-        <v>18</v>
-      </c>
-      <c r="D102" s="46" t="s">
-        <v>421</v>
-      </c>
-      <c r="E102" s="46" t="s">
-        <v>424</v>
-      </c>
-      <c r="F102" s="46" t="s">
-        <v>425</v>
-      </c>
-      <c r="G102" s="47" t="n">
-        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M05.01.01")</f>
-        <v>1</v>
-      </c>
-      <c r="H102" s="50" t="s">
-        <v>35</v>
-      </c>
-      <c r="I102" s="46"/>
-    </row>
-    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="46" t="s">
-        <v>426</v>
-      </c>
-      <c r="B103" s="46" t="s">
-        <v>23</v>
-      </c>
-      <c r="C103" s="46" t="s">
-        <v>18</v>
-      </c>
-      <c r="D103" s="46" t="s">
-        <v>421</v>
-      </c>
-      <c r="E103" s="46" t="s">
-        <v>427</v>
-      </c>
-      <c r="F103" s="46" t="s">
-        <v>428</v>
-      </c>
-      <c r="G103" s="47" t="n">
-        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M05.01.02")</f>
-        <v>1</v>
-      </c>
-      <c r="H103" s="50" t="s">
-        <v>35</v>
-      </c>
-      <c r="I103" s="46"/>
-    </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="46" t="s">
-        <v>429</v>
-      </c>
-      <c r="B104" s="46" t="s">
-        <v>23</v>
-      </c>
-      <c r="C104" s="46" t="s">
-        <v>18</v>
-      </c>
-      <c r="D104" s="46" t="s">
-        <v>421</v>
-      </c>
-      <c r="E104" s="46" t="s">
-        <v>430</v>
-      </c>
-      <c r="F104" s="46" t="s">
-        <v>431</v>
-      </c>
-      <c r="G104" s="47" t="n">
-        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M05.01.03")</f>
-        <v>1</v>
-      </c>
-      <c r="H104" s="50" t="s">
-        <v>35</v>
-      </c>
-      <c r="I104" s="46"/>
-    </row>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="46" t="s">
-        <v>432</v>
-      </c>
-      <c r="B105" s="46" t="s">
-        <v>23</v>
-      </c>
-      <c r="C105" s="46" t="s">
-        <v>18</v>
-      </c>
-      <c r="D105" s="46" t="s">
-        <v>421</v>
-      </c>
-      <c r="E105" s="46" t="s">
-        <v>433</v>
-      </c>
-      <c r="F105" s="46" t="s">
-        <v>434</v>
-      </c>
-      <c r="G105" s="47" t="n">
-        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M05.01.04")</f>
-        <v>1</v>
-      </c>
-      <c r="H105" s="50" t="s">
-        <v>35</v>
-      </c>
-      <c r="I105" s="46"/>
-    </row>
-    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="46" t="s">
-        <v>435</v>
-      </c>
-      <c r="B106" s="46" t="s">
-        <v>23</v>
-      </c>
-      <c r="C106" s="46" t="s">
-        <v>18</v>
-      </c>
-      <c r="D106" s="46" t="s">
-        <v>421</v>
-      </c>
-      <c r="E106" s="46" t="s">
-        <v>436</v>
-      </c>
-      <c r="F106" s="46" t="s">
-        <v>437</v>
-      </c>
-      <c r="G106" s="47" t="n">
-        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M05.01.05")</f>
-        <v>1</v>
-      </c>
-      <c r="H106" s="50" t="s">
-        <v>35</v>
-      </c>
-      <c r="I106" s="46"/>
+      <c r="H106" s="44"/>
+      <c r="I106" s="44"/>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="46" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="B107" s="46" t="s">
         <v>23</v>
@@ -6812,189 +7011,329 @@
         <v>18</v>
       </c>
       <c r="D107" s="46" t="s">
-        <v>421</v>
+        <v>441</v>
       </c>
       <c r="E107" s="46" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="F107" s="46" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="G107" s="47" t="n">
+        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M05.01.01")</f>
+        <v>1</v>
+      </c>
+      <c r="H107" s="50" t="s">
+        <v>35</v>
+      </c>
+      <c r="I107" s="46"/>
+    </row>
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="46" t="s">
+        <v>446</v>
+      </c>
+      <c r="B108" s="46" t="s">
+        <v>23</v>
+      </c>
+      <c r="C108" s="46" t="s">
+        <v>18</v>
+      </c>
+      <c r="D108" s="46" t="s">
+        <v>441</v>
+      </c>
+      <c r="E108" s="46" t="s">
+        <v>447</v>
+      </c>
+      <c r="F108" s="46" t="s">
+        <v>448</v>
+      </c>
+      <c r="G108" s="47" t="n">
+        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M05.01.02")</f>
+        <v>1</v>
+      </c>
+      <c r="H108" s="50" t="s">
+        <v>35</v>
+      </c>
+      <c r="I108" s="46"/>
+    </row>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="46" t="s">
+        <v>449</v>
+      </c>
+      <c r="B109" s="46" t="s">
+        <v>23</v>
+      </c>
+      <c r="C109" s="46" t="s">
+        <v>18</v>
+      </c>
+      <c r="D109" s="46" t="s">
+        <v>441</v>
+      </c>
+      <c r="E109" s="46" t="s">
+        <v>450</v>
+      </c>
+      <c r="F109" s="46" t="s">
+        <v>451</v>
+      </c>
+      <c r="G109" s="47" t="n">
+        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M05.01.03")</f>
+        <v>1</v>
+      </c>
+      <c r="H109" s="50" t="s">
+        <v>35</v>
+      </c>
+      <c r="I109" s="46"/>
+    </row>
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="46" t="s">
+        <v>452</v>
+      </c>
+      <c r="B110" s="46" t="s">
+        <v>23</v>
+      </c>
+      <c r="C110" s="46" t="s">
+        <v>18</v>
+      </c>
+      <c r="D110" s="46" t="s">
+        <v>441</v>
+      </c>
+      <c r="E110" s="46" t="s">
+        <v>453</v>
+      </c>
+      <c r="F110" s="46" t="s">
+        <v>454</v>
+      </c>
+      <c r="G110" s="47" t="n">
+        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M05.01.04")</f>
+        <v>1</v>
+      </c>
+      <c r="H110" s="50" t="s">
+        <v>35</v>
+      </c>
+      <c r="I110" s="46"/>
+    </row>
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="46" t="s">
+        <v>455</v>
+      </c>
+      <c r="B111" s="46" t="s">
+        <v>23</v>
+      </c>
+      <c r="C111" s="46" t="s">
+        <v>18</v>
+      </c>
+      <c r="D111" s="46" t="s">
+        <v>441</v>
+      </c>
+      <c r="E111" s="46" t="s">
+        <v>456</v>
+      </c>
+      <c r="F111" s="46" t="s">
+        <v>457</v>
+      </c>
+      <c r="G111" s="47" t="n">
+        <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M05.01.05")</f>
+        <v>1</v>
+      </c>
+      <c r="H111" s="50" t="s">
+        <v>35</v>
+      </c>
+      <c r="I111" s="46"/>
+    </row>
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="46" t="s">
+        <v>458</v>
+      </c>
+      <c r="B112" s="46" t="s">
+        <v>23</v>
+      </c>
+      <c r="C112" s="46" t="s">
+        <v>18</v>
+      </c>
+      <c r="D112" s="46" t="s">
+        <v>441</v>
+      </c>
+      <c r="E112" s="46" t="s">
+        <v>459</v>
+      </c>
+      <c r="F112" s="46" t="s">
+        <v>460</v>
+      </c>
+      <c r="G112" s="47" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M05.01.06")</f>
         <v>1</v>
       </c>
-      <c r="H107" s="50" t="s">
-        <v>35</v>
-      </c>
-      <c r="I107" s="46"/>
-    </row>
-    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="44" t="s">
-        <v>441</v>
-      </c>
-      <c r="B108" s="44" t="s">
+      <c r="H112" s="50" t="s">
+        <v>35</v>
+      </c>
+      <c r="I112" s="46"/>
+    </row>
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="44" t="s">
+        <v>461</v>
+      </c>
+      <c r="B113" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="C108" s="44" t="s">
+      <c r="C113" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="D108" s="44" t="s">
-        <v>442</v>
-      </c>
-      <c r="E108" s="44"/>
-      <c r="F108" s="44" t="s">
-        <v>443</v>
-      </c>
-      <c r="G108" s="45" t="n">
+      <c r="D113" s="44" t="s">
+        <v>462</v>
+      </c>
+      <c r="E113" s="44"/>
+      <c r="F113" s="44" t="s">
+        <v>463</v>
+      </c>
+      <c r="G113" s="45" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$D:$D,"M05.02")</f>
         <v>5</v>
       </c>
-      <c r="H108" s="44"/>
-      <c r="I108" s="44"/>
-    </row>
-    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="46" t="s">
-        <v>444</v>
-      </c>
-      <c r="B109" s="46" t="s">
+      <c r="H113" s="44"/>
+      <c r="I113" s="44"/>
+    </row>
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="46" t="s">
+        <v>464</v>
+      </c>
+      <c r="B114" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="C109" s="46" t="s">
+      <c r="C114" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="D109" s="46" t="s">
-        <v>442</v>
-      </c>
-      <c r="E109" s="46" t="s">
-        <v>445</v>
-      </c>
-      <c r="F109" s="46" t="s">
-        <v>446</v>
-      </c>
-      <c r="G109" s="47" t="n">
+      <c r="D114" s="46" t="s">
+        <v>462</v>
+      </c>
+      <c r="E114" s="46" t="s">
+        <v>465</v>
+      </c>
+      <c r="F114" s="46" t="s">
+        <v>466</v>
+      </c>
+      <c r="G114" s="47" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M05.02.01")</f>
         <v>1</v>
       </c>
-      <c r="H109" s="50" t="s">
-        <v>35</v>
-      </c>
-      <c r="I109" s="46"/>
-    </row>
-    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="46" t="s">
-        <v>447</v>
-      </c>
-      <c r="B110" s="46" t="s">
+      <c r="H114" s="50" t="s">
+        <v>35</v>
+      </c>
+      <c r="I114" s="46"/>
+    </row>
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="46" t="s">
+        <v>467</v>
+      </c>
+      <c r="B115" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="C110" s="46" t="s">
+      <c r="C115" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="D110" s="46" t="s">
-        <v>442</v>
-      </c>
-      <c r="E110" s="46" t="s">
-        <v>448</v>
-      </c>
-      <c r="F110" s="46" t="s">
-        <v>449</v>
-      </c>
-      <c r="G110" s="47" t="n">
+      <c r="D115" s="46" t="s">
+        <v>462</v>
+      </c>
+      <c r="E115" s="46" t="s">
+        <v>468</v>
+      </c>
+      <c r="F115" s="46" t="s">
+        <v>469</v>
+      </c>
+      <c r="G115" s="47" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M05.02.02")</f>
         <v>1</v>
       </c>
-      <c r="H110" s="50" t="s">
-        <v>35</v>
-      </c>
-      <c r="I110" s="46"/>
-    </row>
-    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="46" t="s">
-        <v>450</v>
-      </c>
-      <c r="B111" s="46" t="s">
+      <c r="H115" s="50" t="s">
+        <v>35</v>
+      </c>
+      <c r="I115" s="46"/>
+    </row>
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="46" t="s">
+        <v>470</v>
+      </c>
+      <c r="B116" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="C111" s="46" t="s">
+      <c r="C116" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="D111" s="46" t="s">
-        <v>442</v>
-      </c>
-      <c r="E111" s="46" t="s">
-        <v>451</v>
-      </c>
-      <c r="F111" s="46" t="s">
-        <v>452</v>
-      </c>
-      <c r="G111" s="47" t="n">
+      <c r="D116" s="46" t="s">
+        <v>462</v>
+      </c>
+      <c r="E116" s="46" t="s">
+        <v>471</v>
+      </c>
+      <c r="F116" s="46" t="s">
+        <v>472</v>
+      </c>
+      <c r="G116" s="47" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M05.02.03")</f>
         <v>1</v>
       </c>
-      <c r="H111" s="50" t="s">
-        <v>35</v>
-      </c>
-      <c r="I111" s="46"/>
-    </row>
-    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="46" t="s">
-        <v>453</v>
-      </c>
-      <c r="B112" s="46" t="s">
+      <c r="H116" s="50" t="s">
+        <v>35</v>
+      </c>
+      <c r="I116" s="46"/>
+    </row>
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="46" t="s">
+        <v>473</v>
+      </c>
+      <c r="B117" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="C112" s="46" t="s">
+      <c r="C117" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="D112" s="46" t="s">
-        <v>442</v>
-      </c>
-      <c r="E112" s="46" t="s">
-        <v>454</v>
-      </c>
-      <c r="F112" s="46" t="s">
-        <v>455</v>
-      </c>
-      <c r="G112" s="47" t="n">
+      <c r="D117" s="46" t="s">
+        <v>462</v>
+      </c>
+      <c r="E117" s="46" t="s">
+        <v>474</v>
+      </c>
+      <c r="F117" s="46" t="s">
+        <v>475</v>
+      </c>
+      <c r="G117" s="47" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M05.02.04")</f>
         <v>1</v>
       </c>
-      <c r="H112" s="50" t="s">
-        <v>35</v>
-      </c>
-      <c r="I112" s="46"/>
-    </row>
-    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="46" t="s">
-        <v>456</v>
-      </c>
-      <c r="B113" s="46" t="s">
+      <c r="H117" s="50" t="s">
+        <v>35</v>
+      </c>
+      <c r="I117" s="46"/>
+    </row>
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="46" t="s">
+        <v>476</v>
+      </c>
+      <c r="B118" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="C113" s="46" t="s">
+      <c r="C118" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="D113" s="46" t="s">
-        <v>442</v>
-      </c>
-      <c r="E113" s="46" t="s">
-        <v>457</v>
-      </c>
-      <c r="F113" s="46" t="s">
-        <v>458</v>
-      </c>
-      <c r="G113" s="47" t="n">
+      <c r="D118" s="46" t="s">
+        <v>462</v>
+      </c>
+      <c r="E118" s="46" t="s">
+        <v>477</v>
+      </c>
+      <c r="F118" s="46" t="s">
+        <v>478</v>
+      </c>
+      <c r="G118" s="47" t="n">
         <f aca="false">COUNTIF('Screen Inventory'!$F:$F,"M05.02.05")</f>
         <v>1</v>
       </c>
-      <c r="H113" s="50" t="s">
-        <v>35</v>
-      </c>
-      <c r="I113" s="46"/>
+      <c r="H118" s="50" t="s">
+        <v>35</v>
+      </c>
+      <c r="I118" s="46"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:I113"/>
+  <autoFilter ref="A4:I118"/>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
@@ -7035,38 +7374,43 @@
     <hyperlink ref="H70" r:id="rId33" display="Open"/>
     <hyperlink ref="H71" r:id="rId34" display="Open"/>
     <hyperlink ref="H72" r:id="rId35" display="Open"/>
-    <hyperlink ref="H74" r:id="rId36" display="Open"/>
-    <hyperlink ref="H76" r:id="rId37" display="Open"/>
-    <hyperlink ref="H77" r:id="rId38" display="Open"/>
-    <hyperlink ref="H78" r:id="rId39" display="Open"/>
-    <hyperlink ref="H79" r:id="rId40" display="Open"/>
-    <hyperlink ref="H80" r:id="rId41" display="Open"/>
+    <hyperlink ref="H73" r:id="rId36" display="Open"/>
+    <hyperlink ref="H74" r:id="rId37" display="Open"/>
+    <hyperlink ref="H75" r:id="rId38" display="Open"/>
+    <hyperlink ref="H76" r:id="rId39" display="Open"/>
+    <hyperlink ref="H77" r:id="rId40" display="Open"/>
+    <hyperlink ref="H79" r:id="rId41" display="Open"/>
     <hyperlink ref="H81" r:id="rId42" display="Open"/>
     <hyperlink ref="H82" r:id="rId43" display="Open"/>
     <hyperlink ref="H83" r:id="rId44" display="Open"/>
     <hyperlink ref="H84" r:id="rId45" display="Open"/>
-    <hyperlink ref="H86" r:id="rId46" display="Open"/>
-    <hyperlink ref="H87" r:id="rId47" display="Open"/>
-    <hyperlink ref="H88" r:id="rId48" display="Open"/>
-    <hyperlink ref="H89" r:id="rId49" display="Open"/>
-    <hyperlink ref="H90" r:id="rId50" display="Open"/>
-    <hyperlink ref="H93" r:id="rId51" display="Open"/>
-    <hyperlink ref="H94" r:id="rId52" display="Open"/>
-    <hyperlink ref="H95" r:id="rId53" display="Open"/>
-    <hyperlink ref="H96" r:id="rId54" display="Open"/>
-    <hyperlink ref="H97" r:id="rId55" display="Open"/>
-    <hyperlink ref="H99" r:id="rId56" display="Open"/>
-    <hyperlink ref="H102" r:id="rId57" display="Open"/>
-    <hyperlink ref="H103" r:id="rId58" display="Open"/>
-    <hyperlink ref="H104" r:id="rId59" display="Open"/>
-    <hyperlink ref="H105" r:id="rId60" display="Open"/>
-    <hyperlink ref="H106" r:id="rId61" display="Open"/>
+    <hyperlink ref="H85" r:id="rId46" display="Open"/>
+    <hyperlink ref="H86" r:id="rId47" display="Open"/>
+    <hyperlink ref="H87" r:id="rId48" display="Open"/>
+    <hyperlink ref="H88" r:id="rId49" display="Open"/>
+    <hyperlink ref="H89" r:id="rId50" display="Open"/>
+    <hyperlink ref="H91" r:id="rId51" display="Open"/>
+    <hyperlink ref="H92" r:id="rId52" display="Open"/>
+    <hyperlink ref="H93" r:id="rId53" display="Open"/>
+    <hyperlink ref="H94" r:id="rId54" display="Open"/>
+    <hyperlink ref="H95" r:id="rId55" display="Open"/>
+    <hyperlink ref="H98" r:id="rId56" display="Open"/>
+    <hyperlink ref="H99" r:id="rId57" display="Open"/>
+    <hyperlink ref="H100" r:id="rId58" display="Open"/>
+    <hyperlink ref="H101" r:id="rId59" display="Open"/>
+    <hyperlink ref="H102" r:id="rId60" display="Open"/>
+    <hyperlink ref="H104" r:id="rId61" display="Open"/>
     <hyperlink ref="H107" r:id="rId62" display="Open"/>
-    <hyperlink ref="H109" r:id="rId63" display="Open"/>
-    <hyperlink ref="H110" r:id="rId64" display="Open"/>
-    <hyperlink ref="H111" r:id="rId65" display="Open"/>
-    <hyperlink ref="H112" r:id="rId66" display="Open"/>
-    <hyperlink ref="H113" r:id="rId67" display="Open"/>
+    <hyperlink ref="H108" r:id="rId63" display="Open"/>
+    <hyperlink ref="H109" r:id="rId64" display="Open"/>
+    <hyperlink ref="H110" r:id="rId65" display="Open"/>
+    <hyperlink ref="H111" r:id="rId66" display="Open"/>
+    <hyperlink ref="H112" r:id="rId67" display="Open"/>
+    <hyperlink ref="H114" r:id="rId68" display="Open"/>
+    <hyperlink ref="H115" r:id="rId69" display="Open"/>
+    <hyperlink ref="H116" r:id="rId70" display="Open"/>
+    <hyperlink ref="H117" r:id="rId71" display="Open"/>
+    <hyperlink ref="H118" r:id="rId72" display="Open"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -7075,7 +7419,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId68"/>
+  <drawing r:id="rId73"/>
 </worksheet>
 </file>
 
@@ -7084,7 +7428,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I87"/>
+  <dimension ref="A1:I93"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -7100,7 +7444,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>459</v>
+        <v>479</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -7113,7 +7457,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>460</v>
+        <v>480</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -7126,7 +7470,7 @@
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>461</v>
+        <v>481</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>2</v>
@@ -7135,22 +7479,22 @@
         <v>3</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>462</v>
+        <v>482</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>22</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>463</v>
+        <v>483</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>464</v>
+        <v>484</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7164,19 +7508,19 @@
         <v>10</v>
       </c>
       <c r="D5" s="46" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="E5" s="46" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="F5" s="46" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="G5" s="46" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="H5" s="46" t="s">
-        <v>465</v>
+        <v>485</v>
       </c>
       <c r="I5" s="50" t="s">
         <v>35</v>
@@ -7193,19 +7537,19 @@
         <v>12</v>
       </c>
       <c r="D6" s="46" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="E6" s="46" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="F6" s="46" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="G6" s="46" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="H6" s="46" t="s">
-        <v>466</v>
+        <v>486</v>
       </c>
       <c r="I6" s="50" t="s">
         <v>35</v>
@@ -7222,19 +7566,19 @@
         <v>12</v>
       </c>
       <c r="D7" s="46" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="E7" s="46" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="F7" s="46" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="G7" s="46" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="H7" s="46" t="s">
-        <v>466</v>
+        <v>486</v>
       </c>
       <c r="I7" s="50" t="s">
         <v>35</v>
@@ -7251,19 +7595,19 @@
         <v>12</v>
       </c>
       <c r="D8" s="46" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="E8" s="46" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="F8" s="46" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="G8" s="46" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="H8" s="46" t="s">
-        <v>467</v>
+        <v>487</v>
       </c>
       <c r="I8" s="50" t="s">
         <v>35</v>
@@ -7280,19 +7624,19 @@
         <v>12</v>
       </c>
       <c r="D9" s="46" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="E9" s="46" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="F9" s="46" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="G9" s="46" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="H9" s="46" t="s">
-        <v>468</v>
+        <v>488</v>
       </c>
       <c r="I9" s="50" t="s">
         <v>35</v>
@@ -7309,19 +7653,19 @@
         <v>12</v>
       </c>
       <c r="D10" s="46" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="E10" s="46" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="F10" s="46" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="G10" s="46" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="H10" s="46" t="s">
-        <v>469</v>
+        <v>489</v>
       </c>
       <c r="I10" s="50" t="s">
         <v>35</v>
@@ -7338,19 +7682,19 @@
         <v>12</v>
       </c>
       <c r="D11" s="46" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="E11" s="46" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="F11" s="46" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="G11" s="46" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="H11" s="46" t="s">
-        <v>470</v>
+        <v>490</v>
       </c>
       <c r="I11" s="50" t="s">
         <v>35</v>
@@ -7367,19 +7711,19 @@
         <v>12</v>
       </c>
       <c r="D12" s="46" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="E12" s="46" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="F12" s="46" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="G12" s="46" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="H12" s="46" t="s">
-        <v>471</v>
+        <v>491</v>
       </c>
       <c r="I12" s="50" t="s">
         <v>35</v>
@@ -7396,19 +7740,19 @@
         <v>12</v>
       </c>
       <c r="D13" s="46" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="E13" s="46" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="F13" s="46" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="G13" s="46" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="H13" s="46" t="s">
-        <v>472</v>
+        <v>492</v>
       </c>
       <c r="I13" s="50" t="s">
         <v>35</v>
@@ -7425,19 +7769,19 @@
         <v>12</v>
       </c>
       <c r="D14" s="46" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="E14" s="46" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="F14" s="46" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="G14" s="46" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="H14" s="46" t="s">
-        <v>473</v>
+        <v>493</v>
       </c>
       <c r="I14" s="50" t="s">
         <v>35</v>
@@ -7454,19 +7798,19 @@
         <v>12</v>
       </c>
       <c r="D15" s="46" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="E15" s="46" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="F15" s="46" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="G15" s="46" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="H15" s="46" t="s">
-        <v>474</v>
+        <v>494</v>
       </c>
       <c r="I15" s="50" t="s">
         <v>35</v>
@@ -7483,19 +7827,19 @@
         <v>12</v>
       </c>
       <c r="D16" s="46" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="E16" s="46" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="F16" s="46" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="G16" s="46" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="H16" s="46" t="s">
-        <v>475</v>
+        <v>495</v>
       </c>
       <c r="I16" s="50" t="s">
         <v>35</v>
@@ -7512,19 +7856,19 @@
         <v>12</v>
       </c>
       <c r="D17" s="46" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="E17" s="46" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="F17" s="46" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="G17" s="46" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="H17" s="46" t="s">
-        <v>475</v>
+        <v>495</v>
       </c>
       <c r="I17" s="50" t="s">
         <v>35</v>
@@ -7541,19 +7885,19 @@
         <v>12</v>
       </c>
       <c r="D18" s="46" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="E18" s="46" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="F18" s="46" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G18" s="46" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="H18" s="46" t="s">
-        <v>476</v>
+        <v>496</v>
       </c>
       <c r="I18" s="50" t="s">
         <v>35</v>
@@ -7570,19 +7914,19 @@
         <v>12</v>
       </c>
       <c r="D19" s="46" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="E19" s="46" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="F19" s="46" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G19" s="46" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="H19" s="46" t="s">
-        <v>477</v>
+        <v>497</v>
       </c>
       <c r="I19" s="50" t="s">
         <v>35</v>
@@ -7599,19 +7943,19 @@
         <v>12</v>
       </c>
       <c r="D20" s="46" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="E20" s="46" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="F20" s="46" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="G20" s="46" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="H20" s="46" t="s">
-        <v>478</v>
+        <v>498</v>
       </c>
       <c r="I20" s="50" t="s">
         <v>35</v>
@@ -7628,19 +7972,19 @@
         <v>12</v>
       </c>
       <c r="D21" s="46" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="E21" s="46" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="F21" s="46" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="G21" s="46" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="H21" s="46" t="s">
-        <v>479</v>
+        <v>499</v>
       </c>
       <c r="I21" s="50" t="s">
         <v>35</v>
@@ -7657,19 +8001,19 @@
         <v>12</v>
       </c>
       <c r="D22" s="46" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="E22" s="46" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="F22" s="46" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="G22" s="46" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="H22" s="46" t="s">
-        <v>480</v>
+        <v>500</v>
       </c>
       <c r="I22" s="50" t="s">
         <v>35</v>
@@ -7686,19 +8030,19 @@
         <v>12</v>
       </c>
       <c r="D23" s="46" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="E23" s="46" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="F23" s="46" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="G23" s="46" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="H23" s="46" t="s">
-        <v>481</v>
+        <v>501</v>
       </c>
       <c r="I23" s="50" t="s">
         <v>35</v>
@@ -7715,19 +8059,19 @@
         <v>12</v>
       </c>
       <c r="D24" s="46" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="E24" s="46" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="F24" s="46" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="G24" s="46" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="H24" s="46" t="s">
-        <v>482</v>
+        <v>502</v>
       </c>
       <c r="I24" s="50" t="s">
         <v>35</v>
@@ -7744,19 +8088,19 @@
         <v>12</v>
       </c>
       <c r="D25" s="46" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="E25" s="46" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="F25" s="46" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="G25" s="46" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="H25" s="46" t="s">
-        <v>483</v>
+        <v>503</v>
       </c>
       <c r="I25" s="50" t="s">
         <v>35</v>
@@ -7773,19 +8117,19 @@
         <v>12</v>
       </c>
       <c r="D26" s="46" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="E26" s="46" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="F26" s="46" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="G26" s="46" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="H26" s="46" t="s">
-        <v>484</v>
+        <v>504</v>
       </c>
       <c r="I26" s="50" t="s">
         <v>35</v>
@@ -7802,19 +8146,19 @@
         <v>12</v>
       </c>
       <c r="D27" s="46" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="E27" s="46" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="F27" s="46" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="G27" s="46" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="H27" s="46" t="s">
-        <v>485</v>
+        <v>505</v>
       </c>
       <c r="I27" s="50" t="s">
         <v>35</v>
@@ -7831,19 +8175,19 @@
         <v>12</v>
       </c>
       <c r="D28" s="46" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="E28" s="46" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="F28" s="46" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="G28" s="46" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="H28" s="46" t="s">
-        <v>486</v>
+        <v>506</v>
       </c>
       <c r="I28" s="50" t="s">
         <v>35</v>
@@ -7860,19 +8204,19 @@
         <v>12</v>
       </c>
       <c r="D29" s="46" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="E29" s="46" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="F29" s="46" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="G29" s="46" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="H29" s="46" t="s">
-        <v>487</v>
+        <v>507</v>
       </c>
       <c r="I29" s="50" t="s">
         <v>35</v>
@@ -7889,19 +8233,19 @@
         <v>12</v>
       </c>
       <c r="D30" s="46" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="E30" s="46" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="F30" s="46" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="G30" s="46" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="H30" s="46" t="s">
-        <v>488</v>
+        <v>508</v>
       </c>
       <c r="I30" s="50" t="s">
         <v>35</v>
@@ -7918,19 +8262,19 @@
         <v>12</v>
       </c>
       <c r="D31" s="46" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="E31" s="46" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="F31" s="46" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="G31" s="46" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="H31" s="46" t="s">
-        <v>489</v>
+        <v>509</v>
       </c>
       <c r="I31" s="50" t="s">
         <v>35</v>
@@ -7947,19 +8291,19 @@
         <v>14</v>
       </c>
       <c r="D32" s="46" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="E32" s="46" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="F32" s="46" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="G32" s="46" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="H32" s="46" t="s">
-        <v>490</v>
+        <v>510</v>
       </c>
       <c r="I32" s="50" t="s">
         <v>35</v>
@@ -7976,19 +8320,19 @@
         <v>14</v>
       </c>
       <c r="D33" s="46" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E33" s="46" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="F33" s="46" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="G33" s="46" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="H33" s="46" t="s">
-        <v>491</v>
+        <v>511</v>
       </c>
       <c r="I33" s="50" t="s">
         <v>35</v>
@@ -8005,19 +8349,19 @@
         <v>14</v>
       </c>
       <c r="D34" s="46" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E34" s="46" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="F34" s="46" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="G34" s="46" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="H34" s="46" t="s">
-        <v>492</v>
+        <v>512</v>
       </c>
       <c r="I34" s="50" t="s">
         <v>35</v>
@@ -8034,19 +8378,19 @@
         <v>14</v>
       </c>
       <c r="D35" s="46" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E35" s="46" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="F35" s="46" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="G35" s="46" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="H35" s="46" t="s">
-        <v>493</v>
+        <v>513</v>
       </c>
       <c r="I35" s="50" t="s">
         <v>35</v>
@@ -8063,19 +8407,19 @@
         <v>14</v>
       </c>
       <c r="D36" s="46" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E36" s="46" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="F36" s="46" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="G36" s="46" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="H36" s="46" t="s">
-        <v>494</v>
+        <v>514</v>
       </c>
       <c r="I36" s="50" t="s">
         <v>35</v>
@@ -8092,19 +8436,19 @@
         <v>14</v>
       </c>
       <c r="D37" s="46" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E37" s="46" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="F37" s="46" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="G37" s="46" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="H37" s="46" t="s">
-        <v>495</v>
+        <v>515</v>
       </c>
       <c r="I37" s="50" t="s">
         <v>35</v>
@@ -8121,19 +8465,19 @@
         <v>14</v>
       </c>
       <c r="D38" s="46" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="E38" s="46" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="F38" s="46" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="G38" s="46" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="H38" s="46" t="s">
-        <v>496</v>
+        <v>516</v>
       </c>
       <c r="I38" s="50" t="s">
         <v>35</v>
@@ -8150,19 +8494,19 @@
         <v>14</v>
       </c>
       <c r="D39" s="46" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="E39" s="46" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="F39" s="46" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="G39" s="46" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="H39" s="46" t="s">
-        <v>497</v>
+        <v>517</v>
       </c>
       <c r="I39" s="50" t="s">
         <v>35</v>
@@ -8179,19 +8523,19 @@
         <v>14</v>
       </c>
       <c r="D40" s="46" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="E40" s="46" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="F40" s="46" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="G40" s="46" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="H40" s="46" t="s">
-        <v>498</v>
+        <v>518</v>
       </c>
       <c r="I40" s="50" t="s">
         <v>35</v>
@@ -8208,19 +8552,19 @@
         <v>14</v>
       </c>
       <c r="D41" s="46" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="E41" s="46" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="F41" s="46" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="G41" s="46" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="H41" s="46" t="s">
-        <v>499</v>
+        <v>519</v>
       </c>
       <c r="I41" s="50" t="s">
         <v>35</v>
@@ -8237,19 +8581,19 @@
         <v>14</v>
       </c>
       <c r="D42" s="46" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="E42" s="46" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="F42" s="46" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="G42" s="46" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="H42" s="46" t="s">
-        <v>500</v>
+        <v>520</v>
       </c>
       <c r="I42" s="50" t="s">
         <v>35</v>
@@ -8266,19 +8610,19 @@
         <v>14</v>
       </c>
       <c r="D43" s="46" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="E43" s="46" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="F43" s="46" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="G43" s="46" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="H43" s="46" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="I43" s="50" t="s">
         <v>35</v>
@@ -8295,19 +8639,19 @@
         <v>14</v>
       </c>
       <c r="D44" s="46" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="E44" s="46" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="F44" s="46" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="G44" s="46" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="H44" s="46" t="s">
-        <v>502</v>
+        <v>522</v>
       </c>
       <c r="I44" s="50" t="s">
         <v>35</v>
@@ -8324,19 +8668,19 @@
         <v>14</v>
       </c>
       <c r="D45" s="46" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="E45" s="46" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="F45" s="46" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="G45" s="46" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="H45" s="46" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="I45" s="50" t="s">
         <v>35</v>
@@ -8353,25 +8697,25 @@
         <v>14</v>
       </c>
       <c r="D46" s="46" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="E46" s="46" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="F46" s="46" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="G46" s="46" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="H46" s="46" t="s">
-        <v>504</v>
+        <v>524</v>
       </c>
       <c r="I46" s="50" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="46" t="n">
         <v>43</v>
       </c>
@@ -8382,25 +8726,25 @@
         <v>14</v>
       </c>
       <c r="D47" s="46" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="E47" s="46" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="F47" s="46" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="G47" s="46" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="H47" s="46" t="s">
-        <v>505</v>
+        <v>525</v>
       </c>
       <c r="I47" s="50" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="46" t="n">
         <v>44</v>
       </c>
@@ -8411,25 +8755,25 @@
         <v>14</v>
       </c>
       <c r="D48" s="46" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="E48" s="46" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="F48" s="46" t="s">
+        <v>342</v>
+      </c>
+      <c r="G48" s="46" t="s">
         <v>343</v>
       </c>
-      <c r="G48" s="46" t="s">
-        <v>344</v>
-      </c>
       <c r="H48" s="46" t="s">
-        <v>506</v>
+        <v>526</v>
       </c>
       <c r="I48" s="50" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="46" t="n">
         <v>45</v>
       </c>
@@ -8440,25 +8784,25 @@
         <v>14</v>
       </c>
       <c r="D49" s="46" t="s">
+        <v>333</v>
+      </c>
+      <c r="E49" s="46" t="s">
+        <v>334</v>
+      </c>
+      <c r="F49" s="46" t="s">
+        <v>345</v>
+      </c>
+      <c r="G49" s="46" t="s">
         <v>346</v>
       </c>
-      <c r="E49" s="46" t="s">
-        <v>347</v>
-      </c>
-      <c r="F49" s="46" t="s">
-        <v>349</v>
-      </c>
-      <c r="G49" s="46" t="s">
-        <v>350</v>
-      </c>
       <c r="H49" s="46" t="s">
-        <v>507</v>
+        <v>527</v>
       </c>
       <c r="I49" s="50" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="46" t="n">
         <v>46</v>
       </c>
@@ -8469,19 +8813,19 @@
         <v>14</v>
       </c>
       <c r="D50" s="46" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="E50" s="46" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="F50" s="46" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="G50" s="46" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="H50" s="46" t="s">
-        <v>508</v>
+        <v>528</v>
       </c>
       <c r="I50" s="50" t="s">
         <v>35</v>
@@ -8498,25 +8842,25 @@
         <v>14</v>
       </c>
       <c r="D51" s="46" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="E51" s="46" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="F51" s="46" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="G51" s="46" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="H51" s="46" t="s">
-        <v>509</v>
+        <v>529</v>
       </c>
       <c r="I51" s="50" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="46" t="n">
         <v>48</v>
       </c>
@@ -8527,25 +8871,25 @@
         <v>14</v>
       </c>
       <c r="D52" s="46" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="E52" s="46" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="F52" s="46" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="G52" s="46" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="H52" s="46" t="s">
-        <v>510</v>
+        <v>530</v>
       </c>
       <c r="I52" s="50" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="46" t="n">
         <v>49</v>
       </c>
@@ -8556,19 +8900,19 @@
         <v>14</v>
       </c>
       <c r="D53" s="46" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="E53" s="46" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="F53" s="46" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="G53" s="46" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="H53" s="46" t="s">
-        <v>511</v>
+        <v>531</v>
       </c>
       <c r="I53" s="50" t="s">
         <v>35</v>
@@ -8585,19 +8929,19 @@
         <v>14</v>
       </c>
       <c r="D54" s="46" t="s">
-        <v>346</v>
+        <v>360</v>
       </c>
       <c r="E54" s="46" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="F54" s="46" t="s">
+        <v>363</v>
+      </c>
+      <c r="G54" s="46" t="s">
         <v>364</v>
       </c>
-      <c r="G54" s="46" t="s">
-        <v>365</v>
-      </c>
       <c r="H54" s="46" t="s">
-        <v>512</v>
+        <v>532</v>
       </c>
       <c r="I54" s="50" t="s">
         <v>35</v>
@@ -8614,19 +8958,19 @@
         <v>14</v>
       </c>
       <c r="D55" s="46" t="s">
-        <v>346</v>
+        <v>366</v>
       </c>
       <c r="E55" s="46" t="s">
-        <v>347</v>
+        <v>367</v>
       </c>
       <c r="F55" s="46" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="G55" s="46" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="H55" s="46" t="s">
-        <v>513</v>
+        <v>533</v>
       </c>
       <c r="I55" s="50" t="s">
         <v>35</v>
@@ -8643,19 +8987,19 @@
         <v>14</v>
       </c>
       <c r="D56" s="46" t="s">
-        <v>346</v>
+        <v>366</v>
       </c>
       <c r="E56" s="46" t="s">
-        <v>347</v>
+        <v>367</v>
       </c>
       <c r="F56" s="46" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="G56" s="46" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="H56" s="46" t="s">
-        <v>514</v>
+        <v>534</v>
       </c>
       <c r="I56" s="50" t="s">
         <v>35</v>
@@ -8672,19 +9016,19 @@
         <v>14</v>
       </c>
       <c r="D57" s="46" t="s">
-        <v>346</v>
+        <v>366</v>
       </c>
       <c r="E57" s="46" t="s">
-        <v>347</v>
+        <v>367</v>
       </c>
       <c r="F57" s="46" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="G57" s="46" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="H57" s="46" t="s">
-        <v>515</v>
+        <v>535</v>
       </c>
       <c r="I57" s="50" t="s">
         <v>35</v>
@@ -8701,19 +9045,19 @@
         <v>14</v>
       </c>
       <c r="D58" s="46" t="s">
-        <v>346</v>
+        <v>366</v>
       </c>
       <c r="E58" s="46" t="s">
-        <v>347</v>
+        <v>367</v>
       </c>
       <c r="F58" s="46" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="G58" s="46" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="H58" s="46" t="s">
-        <v>516</v>
+        <v>536</v>
       </c>
       <c r="I58" s="50" t="s">
         <v>35</v>
@@ -8730,19 +9074,19 @@
         <v>14</v>
       </c>
       <c r="D59" s="46" t="s">
-        <v>346</v>
+        <v>366</v>
       </c>
       <c r="E59" s="46" t="s">
-        <v>347</v>
+        <v>367</v>
       </c>
       <c r="F59" s="46" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="G59" s="46" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="H59" s="46" t="s">
-        <v>517</v>
+        <v>537</v>
       </c>
       <c r="I59" s="50" t="s">
         <v>35</v>
@@ -8759,19 +9103,19 @@
         <v>14</v>
       </c>
       <c r="D60" s="46" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="E60" s="46" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="F60" s="46" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="G60" s="46" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="H60" s="46" t="s">
-        <v>518</v>
+        <v>538</v>
       </c>
       <c r="I60" s="50" t="s">
         <v>35</v>
@@ -8788,19 +9132,19 @@
         <v>14</v>
       </c>
       <c r="D61" s="46" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="E61" s="46" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="F61" s="46" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="G61" s="46" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="H61" s="46" t="s">
-        <v>519</v>
+        <v>539</v>
       </c>
       <c r="I61" s="50" t="s">
         <v>35</v>
@@ -8817,19 +9161,19 @@
         <v>14</v>
       </c>
       <c r="D62" s="46" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="E62" s="46" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="F62" s="46" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="G62" s="46" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="H62" s="46" t="s">
-        <v>520</v>
+        <v>540</v>
       </c>
       <c r="I62" s="50" t="s">
         <v>35</v>
@@ -8846,19 +9190,19 @@
         <v>14</v>
       </c>
       <c r="D63" s="46" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="E63" s="46" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="F63" s="46" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="G63" s="46" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="H63" s="46" t="s">
-        <v>521</v>
+        <v>541</v>
       </c>
       <c r="I63" s="50" t="s">
         <v>35</v>
@@ -8875,19 +9219,19 @@
         <v>14</v>
       </c>
       <c r="D64" s="46" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="E64" s="46" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="F64" s="46" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="G64" s="46" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="H64" s="46" t="s">
-        <v>522</v>
+        <v>542</v>
       </c>
       <c r="I64" s="50" t="s">
         <v>35</v>
@@ -8904,19 +9248,19 @@
         <v>14</v>
       </c>
       <c r="D65" s="46" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="E65" s="46" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="F65" s="46" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="G65" s="46" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="H65" s="46" t="s">
-        <v>523</v>
+        <v>543</v>
       </c>
       <c r="I65" s="50" t="s">
         <v>35</v>
@@ -8933,19 +9277,19 @@
         <v>14</v>
       </c>
       <c r="D66" s="46" t="s">
-        <v>376</v>
+        <v>396</v>
       </c>
       <c r="E66" s="46" t="s">
-        <v>377</v>
+        <v>397</v>
       </c>
       <c r="F66" s="46" t="s">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="G66" s="46" t="s">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="H66" s="46" t="s">
-        <v>524</v>
+        <v>544</v>
       </c>
       <c r="I66" s="50" t="s">
         <v>35</v>
@@ -8962,19 +9306,19 @@
         <v>14</v>
       </c>
       <c r="D67" s="46" t="s">
-        <v>376</v>
+        <v>396</v>
       </c>
       <c r="E67" s="46" t="s">
-        <v>377</v>
+        <v>397</v>
       </c>
       <c r="F67" s="46" t="s">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="G67" s="46" t="s">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="H67" s="46" t="s">
-        <v>525</v>
+        <v>545</v>
       </c>
       <c r="I67" s="50" t="s">
         <v>35</v>
@@ -8991,19 +9335,19 @@
         <v>14</v>
       </c>
       <c r="D68" s="46" t="s">
-        <v>376</v>
+        <v>396</v>
       </c>
       <c r="E68" s="46" t="s">
-        <v>377</v>
+        <v>397</v>
       </c>
       <c r="F68" s="46" t="s">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="G68" s="46" t="s">
-        <v>392</v>
+        <v>403</v>
       </c>
       <c r="H68" s="46" t="s">
-        <v>526</v>
+        <v>546</v>
       </c>
       <c r="I68" s="50" t="s">
         <v>35</v>
@@ -9020,19 +9364,19 @@
         <v>14</v>
       </c>
       <c r="D69" s="46" t="s">
-        <v>376</v>
+        <v>396</v>
       </c>
       <c r="E69" s="46" t="s">
-        <v>377</v>
+        <v>397</v>
       </c>
       <c r="F69" s="46" t="s">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="G69" s="46" t="s">
-        <v>392</v>
+        <v>403</v>
       </c>
       <c r="H69" s="46" t="s">
-        <v>527</v>
+        <v>547</v>
       </c>
       <c r="I69" s="50" t="s">
         <v>35</v>
@@ -9049,19 +9393,19 @@
         <v>14</v>
       </c>
       <c r="D70" s="46" t="s">
-        <v>376</v>
+        <v>396</v>
       </c>
       <c r="E70" s="46" t="s">
-        <v>377</v>
+        <v>397</v>
       </c>
       <c r="F70" s="46" t="s">
-        <v>391</v>
+        <v>405</v>
       </c>
       <c r="G70" s="46" t="s">
-        <v>392</v>
+        <v>406</v>
       </c>
       <c r="H70" s="46" t="s">
-        <v>528</v>
+        <v>548</v>
       </c>
       <c r="I70" s="50" t="s">
         <v>35</v>
@@ -9072,25 +9416,25 @@
         <v>67</v>
       </c>
       <c r="B71" s="46" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C71" s="46" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D71" s="46" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E71" s="46" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F71" s="46" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="G71" s="46" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="H71" s="46" t="s">
-        <v>529</v>
+        <v>549</v>
       </c>
       <c r="I71" s="50" t="s">
         <v>35</v>
@@ -9101,25 +9445,25 @@
         <v>68</v>
       </c>
       <c r="B72" s="46" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C72" s="46" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D72" s="46" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E72" s="46" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F72" s="46" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="G72" s="46" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="H72" s="46" t="s">
-        <v>530</v>
+        <v>550</v>
       </c>
       <c r="I72" s="50" t="s">
         <v>35</v>
@@ -9130,25 +9474,25 @@
         <v>69</v>
       </c>
       <c r="B73" s="46" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C73" s="46" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D73" s="46" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E73" s="46" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F73" s="46" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="G73" s="46" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="H73" s="46" t="s">
-        <v>531</v>
+        <v>551</v>
       </c>
       <c r="I73" s="50" t="s">
         <v>35</v>
@@ -9159,25 +9503,25 @@
         <v>70</v>
       </c>
       <c r="B74" s="46" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C74" s="46" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D74" s="46" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E74" s="46" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F74" s="46" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="G74" s="46" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="H74" s="46" t="s">
-        <v>532</v>
+        <v>552</v>
       </c>
       <c r="I74" s="50" t="s">
         <v>35</v>
@@ -9188,25 +9532,25 @@
         <v>71</v>
       </c>
       <c r="B75" s="46" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C75" s="46" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D75" s="46" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E75" s="46" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F75" s="46" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="G75" s="46" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H75" s="46" t="s">
-        <v>533</v>
+        <v>553</v>
       </c>
       <c r="I75" s="50" t="s">
         <v>35</v>
@@ -9217,25 +9561,25 @@
         <v>72</v>
       </c>
       <c r="B76" s="46" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C76" s="46" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D76" s="46" t="s">
-        <v>413</v>
+        <v>396</v>
       </c>
       <c r="E76" s="46" t="s">
-        <v>414</v>
+        <v>397</v>
       </c>
       <c r="F76" s="46" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="G76" s="46" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="H76" s="46" t="s">
-        <v>534</v>
+        <v>554</v>
       </c>
       <c r="I76" s="50" t="s">
         <v>35</v>
@@ -9246,25 +9590,25 @@
         <v>73</v>
       </c>
       <c r="B77" s="46" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C77" s="46" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D77" s="46" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="E77" s="46" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="F77" s="46" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="G77" s="46" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="H77" s="46" t="s">
-        <v>535</v>
+        <v>555</v>
       </c>
       <c r="I77" s="50" t="s">
         <v>35</v>
@@ -9275,25 +9619,25 @@
         <v>74</v>
       </c>
       <c r="B78" s="46" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C78" s="46" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D78" s="46" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="E78" s="46" t="s">
+        <v>416</v>
+      </c>
+      <c r="F78" s="46" t="s">
         <v>421</v>
       </c>
-      <c r="F78" s="46" t="s">
-        <v>426</v>
-      </c>
       <c r="G78" s="46" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="H78" s="46" t="s">
-        <v>536</v>
+        <v>556</v>
       </c>
       <c r="I78" s="50" t="s">
         <v>35</v>
@@ -9304,25 +9648,25 @@
         <v>75</v>
       </c>
       <c r="B79" s="46" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C79" s="46" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D79" s="46" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="E79" s="46" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="F79" s="46" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="G79" s="46" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="H79" s="46" t="s">
-        <v>537</v>
+        <v>557</v>
       </c>
       <c r="I79" s="50" t="s">
         <v>35</v>
@@ -9333,25 +9677,25 @@
         <v>76</v>
       </c>
       <c r="B80" s="46" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C80" s="46" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D80" s="46" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="E80" s="46" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="F80" s="46" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="G80" s="46" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="H80" s="46" t="s">
-        <v>538</v>
+        <v>558</v>
       </c>
       <c r="I80" s="50" t="s">
         <v>35</v>
@@ -9362,25 +9706,25 @@
         <v>77</v>
       </c>
       <c r="B81" s="46" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C81" s="46" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D81" s="46" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="E81" s="46" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="F81" s="46" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="G81" s="46" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="H81" s="46" t="s">
-        <v>539</v>
+        <v>559</v>
       </c>
       <c r="I81" s="50" t="s">
         <v>35</v>
@@ -9391,25 +9735,25 @@
         <v>78</v>
       </c>
       <c r="B82" s="46" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C82" s="46" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D82" s="46" t="s">
-        <v>420</v>
+        <v>433</v>
       </c>
       <c r="E82" s="46" t="s">
-        <v>421</v>
+        <v>434</v>
       </c>
       <c r="F82" s="46" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="G82" s="46" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="H82" s="46" t="s">
-        <v>540</v>
+        <v>560</v>
       </c>
       <c r="I82" s="50" t="s">
         <v>35</v>
@@ -9426,19 +9770,19 @@
         <v>18</v>
       </c>
       <c r="D83" s="46" t="s">
+        <v>440</v>
+      </c>
+      <c r="E83" s="46" t="s">
         <v>441</v>
       </c>
-      <c r="E83" s="46" t="s">
-        <v>442</v>
-      </c>
       <c r="F83" s="46" t="s">
+        <v>443</v>
+      </c>
+      <c r="G83" s="46" t="s">
         <v>444</v>
       </c>
-      <c r="G83" s="46" t="s">
-        <v>445</v>
-      </c>
       <c r="H83" s="46" t="s">
-        <v>541</v>
+        <v>561</v>
       </c>
       <c r="I83" s="50" t="s">
         <v>35</v>
@@ -9455,19 +9799,19 @@
         <v>18</v>
       </c>
       <c r="D84" s="46" t="s">
+        <v>440</v>
+      </c>
+      <c r="E84" s="46" t="s">
         <v>441</v>
       </c>
-      <c r="E84" s="46" t="s">
-        <v>442</v>
-      </c>
       <c r="F84" s="46" t="s">
+        <v>446</v>
+      </c>
+      <c r="G84" s="46" t="s">
         <v>447</v>
       </c>
-      <c r="G84" s="46" t="s">
-        <v>448</v>
-      </c>
       <c r="H84" s="46" t="s">
-        <v>542</v>
+        <v>562</v>
       </c>
       <c r="I84" s="50" t="s">
         <v>35</v>
@@ -9484,19 +9828,19 @@
         <v>18</v>
       </c>
       <c r="D85" s="46" t="s">
+        <v>440</v>
+      </c>
+      <c r="E85" s="46" t="s">
         <v>441</v>
       </c>
-      <c r="E85" s="46" t="s">
-        <v>442</v>
-      </c>
       <c r="F85" s="46" t="s">
+        <v>449</v>
+      </c>
+      <c r="G85" s="46" t="s">
         <v>450</v>
       </c>
-      <c r="G85" s="46" t="s">
-        <v>451</v>
-      </c>
       <c r="H85" s="46" t="s">
-        <v>543</v>
+        <v>563</v>
       </c>
       <c r="I85" s="50" t="s">
         <v>35</v>
@@ -9513,19 +9857,19 @@
         <v>18</v>
       </c>
       <c r="D86" s="46" t="s">
+        <v>440</v>
+      </c>
+      <c r="E86" s="46" t="s">
         <v>441</v>
       </c>
-      <c r="E86" s="46" t="s">
-        <v>442</v>
-      </c>
       <c r="F86" s="46" t="s">
+        <v>452</v>
+      </c>
+      <c r="G86" s="46" t="s">
         <v>453</v>
       </c>
-      <c r="G86" s="46" t="s">
-        <v>454</v>
-      </c>
       <c r="H86" s="46" t="s">
-        <v>544</v>
+        <v>564</v>
       </c>
       <c r="I86" s="50" t="s">
         <v>35</v>
@@ -9542,26 +9886,200 @@
         <v>18</v>
       </c>
       <c r="D87" s="46" t="s">
+        <v>440</v>
+      </c>
+      <c r="E87" s="46" t="s">
         <v>441</v>
       </c>
-      <c r="E87" s="46" t="s">
-        <v>442</v>
-      </c>
       <c r="F87" s="46" t="s">
+        <v>455</v>
+      </c>
+      <c r="G87" s="46" t="s">
         <v>456</v>
       </c>
-      <c r="G87" s="46" t="s">
-        <v>457</v>
-      </c>
       <c r="H87" s="46" t="s">
-        <v>545</v>
+        <v>565</v>
       </c>
       <c r="I87" s="50" t="s">
         <v>35</v>
       </c>
     </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="46" t="n">
+        <v>84</v>
+      </c>
+      <c r="B88" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="C88" s="46" t="s">
+        <v>18</v>
+      </c>
+      <c r="D88" s="46" t="s">
+        <v>440</v>
+      </c>
+      <c r="E88" s="46" t="s">
+        <v>441</v>
+      </c>
+      <c r="F88" s="46" t="s">
+        <v>458</v>
+      </c>
+      <c r="G88" s="46" t="s">
+        <v>459</v>
+      </c>
+      <c r="H88" s="46" t="s">
+        <v>566</v>
+      </c>
+      <c r="I88" s="50" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="46" t="n">
+        <v>85</v>
+      </c>
+      <c r="B89" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="C89" s="46" t="s">
+        <v>18</v>
+      </c>
+      <c r="D89" s="46" t="s">
+        <v>461</v>
+      </c>
+      <c r="E89" s="46" t="s">
+        <v>462</v>
+      </c>
+      <c r="F89" s="46" t="s">
+        <v>464</v>
+      </c>
+      <c r="G89" s="46" t="s">
+        <v>465</v>
+      </c>
+      <c r="H89" s="46" t="s">
+        <v>567</v>
+      </c>
+      <c r="I89" s="50" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="46" t="n">
+        <v>86</v>
+      </c>
+      <c r="B90" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="C90" s="46" t="s">
+        <v>18</v>
+      </c>
+      <c r="D90" s="46" t="s">
+        <v>461</v>
+      </c>
+      <c r="E90" s="46" t="s">
+        <v>462</v>
+      </c>
+      <c r="F90" s="46" t="s">
+        <v>467</v>
+      </c>
+      <c r="G90" s="46" t="s">
+        <v>468</v>
+      </c>
+      <c r="H90" s="46" t="s">
+        <v>568</v>
+      </c>
+      <c r="I90" s="50" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="46" t="n">
+        <v>87</v>
+      </c>
+      <c r="B91" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="C91" s="46" t="s">
+        <v>18</v>
+      </c>
+      <c r="D91" s="46" t="s">
+        <v>461</v>
+      </c>
+      <c r="E91" s="46" t="s">
+        <v>462</v>
+      </c>
+      <c r="F91" s="46" t="s">
+        <v>470</v>
+      </c>
+      <c r="G91" s="46" t="s">
+        <v>471</v>
+      </c>
+      <c r="H91" s="46" t="s">
+        <v>569</v>
+      </c>
+      <c r="I91" s="50" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="46" t="n">
+        <v>88</v>
+      </c>
+      <c r="B92" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="C92" s="46" t="s">
+        <v>18</v>
+      </c>
+      <c r="D92" s="46" t="s">
+        <v>461</v>
+      </c>
+      <c r="E92" s="46" t="s">
+        <v>462</v>
+      </c>
+      <c r="F92" s="46" t="s">
+        <v>473</v>
+      </c>
+      <c r="G92" s="46" t="s">
+        <v>474</v>
+      </c>
+      <c r="H92" s="46" t="s">
+        <v>570</v>
+      </c>
+      <c r="I92" s="50" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="46" t="n">
+        <v>89</v>
+      </c>
+      <c r="B93" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="C93" s="46" t="s">
+        <v>18</v>
+      </c>
+      <c r="D93" s="46" t="s">
+        <v>461</v>
+      </c>
+      <c r="E93" s="46" t="s">
+        <v>462</v>
+      </c>
+      <c r="F93" s="46" t="s">
+        <v>476</v>
+      </c>
+      <c r="G93" s="46" t="s">
+        <v>477</v>
+      </c>
+      <c r="H93" s="46" t="s">
+        <v>571</v>
+      </c>
+      <c r="I93" s="50" t="s">
+        <v>35</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:I87"/>
+  <autoFilter ref="A4:I93"/>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
@@ -9650,6 +10168,12 @@
     <hyperlink ref="I85" r:id="rId81" display="Open"/>
     <hyperlink ref="I86" r:id="rId82" display="Open"/>
     <hyperlink ref="I87" r:id="rId83" display="Open"/>
+    <hyperlink ref="I88" r:id="rId84" display="Open"/>
+    <hyperlink ref="I89" r:id="rId85" display="Open"/>
+    <hyperlink ref="I90" r:id="rId86" display="Open"/>
+    <hyperlink ref="I91" r:id="rId87" display="Open"/>
+    <hyperlink ref="I92" r:id="rId88" display="Open"/>
+    <hyperlink ref="I93" r:id="rId89" display="Open"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -9658,6 +10182,121 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId84"/>
+  <drawing r:id="rId90"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="90"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>574</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="46" t="s">
+        <v>578</v>
+      </c>
+      <c r="B5" s="46" t="s">
+        <v>579</v>
+      </c>
+      <c r="C5" s="46" t="s">
+        <v>580</v>
+      </c>
+      <c r="D5" s="46" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="46" t="s">
+        <v>578</v>
+      </c>
+      <c r="B6" s="46" t="s">
+        <v>582</v>
+      </c>
+      <c r="C6" s="46" t="s">
+        <v>580</v>
+      </c>
+      <c r="D6" s="46" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="46" t="s">
+        <v>578</v>
+      </c>
+      <c r="B7" s="46" t="s">
+        <v>582</v>
+      </c>
+      <c r="C7" s="46" t="s">
+        <v>584</v>
+      </c>
+      <c r="D7" s="46" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="46" t="s">
+        <v>578</v>
+      </c>
+      <c r="B8" s="46" t="s">
+        <v>582</v>
+      </c>
+      <c r="C8" s="46" t="s">
+        <v>584</v>
+      </c>
+      <c r="D8" s="46" t="s">
+        <v>586</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>